--- a/Materials.xlsx
+++ b/Materials.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3673FDA2-9D5D-47DA-A161-A3190E02B77D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8CE82AF-B7F6-453B-97B6-BE01B9232FE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="4290" windowWidth="38175" windowHeight="15240" xr2:uid="{A6ACE955-0C4C-4110-BBCD-1B981A886B38}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" activeTab="1" xr2:uid="{A6ACE955-0C4C-4110-BBCD-1B981A886B38}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -2058,13 +2058,19 @@
     <numFmt numFmtId="164" formatCode="#,##0.0;\(#,##0.0\)"/>
     <numFmt numFmtId="165" formatCode="#,##0;\(#,##0\)"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
@@ -2075,13 +2081,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -2089,10 +2088,24 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -2157,15 +2170,17 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2173,20 +2188,20 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2646,87 +2661,87 @@
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2736,14 +2751,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E7B3C00-FF04-4982-B10E-CD93454556D9}">
   <dimension ref="A1:AS499"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.28515625" customWidth="1"/>
-    <col min="2" max="2" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.28515625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="27.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.140625" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="4" t="s">
         <v>63</v>
       </c>
       <c r="B1" s="3"/>
@@ -2841,38 +2857,38 @@
       <c r="AS2" s="3"/>
     </row>
     <row r="3" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="K3" s="7"/>
-      <c r="L3" s="8"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="10"/>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>
@@ -2908,10 +2924,10 @@
       <c r="AS3" s="3"/>
     </row>
     <row r="4" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A4" s="9">
+      <c r="A4" s="11">
         <v>1</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="3" t="s">
@@ -2977,11 +2993,11 @@
       <c r="AS4" s="3"/>
     </row>
     <row r="5" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A5" s="9">
+      <c r="A5" s="11">
         <f>1+A4</f>
         <v>2</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="4" t="s">
         <v>16</v>
       </c>
       <c r="C5" s="3" t="s">
@@ -3033,7 +3049,7 @@
       <c r="AS5" s="3"/>
     </row>
     <row r="6" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A6" s="9">
+      <c r="A6" s="11">
         <f t="shared" ref="A6:A49" si="0">1+A5</f>
         <v>3</v>
       </c>
@@ -3085,7 +3101,7 @@
       <c r="AS6" s="3"/>
     </row>
     <row r="7" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A7" s="9">
+      <c r="A7" s="11">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -3137,11 +3153,11 @@
       <c r="AS7" s="3"/>
     </row>
     <row r="8" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A8" s="9">
+      <c r="A8" s="11">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="4" t="s">
         <v>19</v>
       </c>
       <c r="C8" s="3" t="s">
@@ -3193,7 +3209,7 @@
       <c r="AS8" s="3"/>
     </row>
     <row r="9" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A9" s="9">
+      <c r="A9" s="11">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
@@ -3245,7 +3261,7 @@
       <c r="AS9" s="3"/>
     </row>
     <row r="10" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A10" s="9">
+      <c r="A10" s="11">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
@@ -3297,7 +3313,7 @@
       <c r="AS10" s="3"/>
     </row>
     <row r="11" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A11" s="9">
+      <c r="A11" s="11">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
@@ -3349,7 +3365,7 @@
       <c r="AS11" s="3"/>
     </row>
     <row r="12" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A12" s="9">
+      <c r="A12" s="11">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
@@ -3401,7 +3417,7 @@
       <c r="AS12" s="3"/>
     </row>
     <row r="13" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A13" s="9">
+      <c r="A13" s="11">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -3453,7 +3469,7 @@
       <c r="AS13" s="3"/>
     </row>
     <row r="14" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A14" s="9">
+      <c r="A14" s="11">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
@@ -3505,11 +3521,11 @@
       <c r="AS14" s="3"/>
     </row>
     <row r="15" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A15" s="9">
+      <c r="A15" s="11">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="4" t="s">
         <v>27</v>
       </c>
       <c r="C15" s="3" t="s">
@@ -3575,7 +3591,7 @@
       <c r="AS15" s="3"/>
     </row>
     <row r="16" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A16" s="9">
+      <c r="A16" s="11">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
@@ -3627,7 +3643,7 @@
       <c r="AS16" s="3"/>
     </row>
     <row r="17" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A17" s="9">
+      <c r="A17" s="11">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
@@ -3679,7 +3695,7 @@
       <c r="AS17" s="3"/>
     </row>
     <row r="18" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A18" s="9">
+      <c r="A18" s="11">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
@@ -3731,7 +3747,7 @@
       <c r="AS18" s="3"/>
     </row>
     <row r="19" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A19" s="9">
+      <c r="A19" s="11">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
@@ -3783,7 +3799,7 @@
       <c r="AS19" s="3"/>
     </row>
     <row r="20" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A20" s="9">
+      <c r="A20" s="11">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
@@ -3835,7 +3851,7 @@
       <c r="AS20" s="3"/>
     </row>
     <row r="21" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A21" s="9">
+      <c r="A21" s="11">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
@@ -3887,7 +3903,7 @@
       <c r="AS21" s="3"/>
     </row>
     <row r="22" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A22" s="9">
+      <c r="A22" s="11">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
@@ -3939,7 +3955,7 @@
       <c r="AS22" s="3"/>
     </row>
     <row r="23" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A23" s="9">
+      <c r="A23" s="11">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
@@ -3991,7 +4007,7 @@
       <c r="AS23" s="3"/>
     </row>
     <row r="24" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A24" s="9">
+      <c r="A24" s="11">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
@@ -4043,7 +4059,7 @@
       <c r="AS24" s="3"/>
     </row>
     <row r="25" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A25" s="9">
+      <c r="A25" s="11">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
@@ -4095,7 +4111,7 @@
       <c r="AS25" s="3"/>
     </row>
     <row r="26" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A26" s="9">
+      <c r="A26" s="11">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
@@ -4147,7 +4163,7 @@
       <c r="AS26" s="3"/>
     </row>
     <row r="27" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A27" s="9">
+      <c r="A27" s="11">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
@@ -4199,7 +4215,7 @@
       <c r="AS27" s="3"/>
     </row>
     <row r="28" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A28" s="9">
+      <c r="A28" s="11">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
@@ -4251,7 +4267,7 @@
       <c r="AS28" s="3"/>
     </row>
     <row r="29" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A29" s="9">
+      <c r="A29" s="11">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
@@ -4303,7 +4319,7 @@
       <c r="AS29" s="3"/>
     </row>
     <row r="30" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A30" s="9">
+      <c r="A30" s="11">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
@@ -4355,7 +4371,7 @@
       <c r="AS30" s="3"/>
     </row>
     <row r="31" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A31" s="9">
+      <c r="A31" s="11">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
@@ -4407,7 +4423,7 @@
       <c r="AS31" s="3"/>
     </row>
     <row r="32" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A32" s="9">
+      <c r="A32" s="11">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
@@ -4459,7 +4475,7 @@
       <c r="AS32" s="3"/>
     </row>
     <row r="33" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A33" s="9">
+      <c r="A33" s="11">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
@@ -4511,7 +4527,7 @@
       <c r="AS33" s="3"/>
     </row>
     <row r="34" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A34" s="9">
+      <c r="A34" s="11">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
@@ -4563,7 +4579,7 @@
       <c r="AS34" s="3"/>
     </row>
     <row r="35" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A35" s="9">
+      <c r="A35" s="11">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
@@ -4615,7 +4631,7 @@
       <c r="AS35" s="3"/>
     </row>
     <row r="36" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A36" s="9">
+      <c r="A36" s="11">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
@@ -4667,7 +4683,7 @@
       <c r="AS36" s="3"/>
     </row>
     <row r="37" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A37" s="9">
+      <c r="A37" s="11">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
@@ -4719,7 +4735,7 @@
       <c r="AS37" s="3"/>
     </row>
     <row r="38" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A38" s="9">
+      <c r="A38" s="11">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
@@ -4771,7 +4787,7 @@
       <c r="AS38" s="3"/>
     </row>
     <row r="39" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A39" s="9">
+      <c r="A39" s="11">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
@@ -4823,7 +4839,7 @@
       <c r="AS39" s="3"/>
     </row>
     <row r="40" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A40" s="9">
+      <c r="A40" s="11">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
@@ -4875,7 +4891,7 @@
       <c r="AS40" s="3"/>
     </row>
     <row r="41" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A41" s="9">
+      <c r="A41" s="11">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
@@ -4927,7 +4943,7 @@
       <c r="AS41" s="3"/>
     </row>
     <row r="42" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A42" s="9">
+      <c r="A42" s="11">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
@@ -4979,7 +4995,7 @@
       <c r="AS42" s="3"/>
     </row>
     <row r="43" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A43" s="9">
+      <c r="A43" s="11">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
@@ -5031,7 +5047,7 @@
       <c r="AS43" s="3"/>
     </row>
     <row r="44" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A44" s="9">
+      <c r="A44" s="11">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
@@ -5083,7 +5099,7 @@
       <c r="AS44" s="3"/>
     </row>
     <row r="45" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A45" s="9">
+      <c r="A45" s="11">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
@@ -5135,7 +5151,7 @@
       <c r="AS45" s="3"/>
     </row>
     <row r="46" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A46" s="9">
+      <c r="A46" s="11">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
@@ -5187,7 +5203,7 @@
       <c r="AS46" s="3"/>
     </row>
     <row r="47" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A47" s="9">
+      <c r="A47" s="11">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
@@ -5239,7 +5255,7 @@
       <c r="AS47" s="3"/>
     </row>
     <row r="48" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A48" s="9">
+      <c r="A48" s="11">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
@@ -5291,7 +5307,7 @@
       <c r="AS48" s="3"/>
     </row>
     <row r="49" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A49" s="9">
+      <c r="A49" s="11">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
@@ -26516,7 +26532,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="4" t="s">
         <v>64</v>
       </c>
       <c r="B1" s="3"/>
@@ -26562,38 +26578,38 @@
       <c r="S2" s="3"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="K3" s="7"/>
-      <c r="L3" s="8"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="10"/>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>
@@ -26603,7 +26619,7 @@
       <c r="S3" s="3"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" s="9">
+      <c r="A4" s="11">
         <v>1</v>
       </c>
       <c r="B4" s="3" t="s">
@@ -26632,7 +26648,7 @@
       <c r="S4" s="3"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A5" s="9">
+      <c r="A5" s="11">
         <f>1+A4</f>
         <v>2</v>
       </c>
@@ -26662,7 +26678,7 @@
       <c r="S5" s="3"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A6" s="9">
+      <c r="A6" s="11">
         <f t="shared" ref="A6:A69" si="0">1+A5</f>
         <v>3</v>
       </c>
@@ -26692,11 +26708,11 @@
       <c r="S6" s="3"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A7" s="9">
+      <c r="A7" s="11">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="4" t="s">
         <v>75</v>
       </c>
       <c r="C7" s="3" t="s">
@@ -26721,7 +26737,7 @@
         <f>+F7+G7</f>
         <v>84203.101320499991</v>
       </c>
-      <c r="I7" s="10" t="s">
+      <c r="I7" s="15" t="s">
         <v>667</v>
       </c>
       <c r="J7" s="3"/>
@@ -26736,7 +26752,7 @@
       <c r="S7" s="3"/>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A8" s="9">
+      <c r="A8" s="11">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -26766,7 +26782,7 @@
       <c r="S8" s="3"/>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A9" s="9">
+      <c r="A9" s="11">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
@@ -26796,7 +26812,7 @@
       <c r="S9" s="3"/>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A10" s="9">
+      <c r="A10" s="11">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
@@ -26826,7 +26842,7 @@
       <c r="S10" s="3"/>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A11" s="9">
+      <c r="A11" s="11">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
@@ -26856,7 +26872,7 @@
       <c r="S11" s="3"/>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A12" s="9">
+      <c r="A12" s="11">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
@@ -26886,7 +26902,7 @@
       <c r="S12" s="3"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A13" s="9">
+      <c r="A13" s="11">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -26916,7 +26932,7 @@
       <c r="S13" s="3"/>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A14" s="9">
+      <c r="A14" s="11">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
@@ -26946,7 +26962,7 @@
       <c r="S14" s="3"/>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A15" s="9">
+      <c r="A15" s="11">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
@@ -26976,7 +26992,7 @@
       <c r="S15" s="3"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A16" s="9">
+      <c r="A16" s="11">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
@@ -27006,7 +27022,7 @@
       <c r="S16" s="3"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A17" s="9">
+      <c r="A17" s="11">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
@@ -27036,7 +27052,7 @@
       <c r="S17" s="3"/>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A18" s="9">
+      <c r="A18" s="11">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
@@ -27066,7 +27082,7 @@
       <c r="S18" s="3"/>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A19" s="9">
+      <c r="A19" s="11">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
@@ -27096,7 +27112,7 @@
       <c r="S19" s="3"/>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A20" s="9">
+      <c r="A20" s="11">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
@@ -27126,7 +27142,7 @@
       <c r="S20" s="3"/>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A21" s="9">
+      <c r="A21" s="11">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
@@ -27156,7 +27172,7 @@
       <c r="S21" s="3"/>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A22" s="9">
+      <c r="A22" s="11">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
@@ -27186,7 +27202,7 @@
       <c r="S22" s="3"/>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A23" s="9">
+      <c r="A23" s="11">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
@@ -27216,7 +27232,7 @@
       <c r="S23" s="3"/>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A24" s="9">
+      <c r="A24" s="11">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
@@ -27246,7 +27262,7 @@
       <c r="S24" s="3"/>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A25" s="9">
+      <c r="A25" s="11">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
@@ -27276,7 +27292,7 @@
       <c r="S25" s="3"/>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A26" s="9">
+      <c r="A26" s="11">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
@@ -27306,7 +27322,7 @@
       <c r="S26" s="3"/>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A27" s="9">
+      <c r="A27" s="11">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
@@ -27336,7 +27352,7 @@
       <c r="S27" s="3"/>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A28" s="9">
+      <c r="A28" s="11">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
@@ -27366,7 +27382,7 @@
       <c r="S28" s="3"/>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A29" s="9">
+      <c r="A29" s="11">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
@@ -27396,7 +27412,7 @@
       <c r="S29" s="3"/>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A30" s="9">
+      <c r="A30" s="11">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
@@ -27426,7 +27442,7 @@
       <c r="S30" s="3"/>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A31" s="9">
+      <c r="A31" s="11">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
@@ -27456,7 +27472,7 @@
       <c r="S31" s="3"/>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A32" s="9">
+      <c r="A32" s="11">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
@@ -27486,7 +27502,7 @@
       <c r="S32" s="3"/>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A33" s="9">
+      <c r="A33" s="11">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
@@ -27516,7 +27532,7 @@
       <c r="S33" s="3"/>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A34" s="9">
+      <c r="A34" s="11">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
@@ -27546,7 +27562,7 @@
       <c r="S34" s="3"/>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A35" s="9">
+      <c r="A35" s="11">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
@@ -27576,7 +27592,7 @@
       <c r="S35" s="3"/>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A36" s="9">
+      <c r="A36" s="11">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
@@ -27606,7 +27622,7 @@
       <c r="S36" s="3"/>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A37" s="9">
+      <c r="A37" s="11">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
@@ -27636,7 +27652,7 @@
       <c r="S37" s="3"/>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A38" s="9">
+      <c r="A38" s="11">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
@@ -27666,7 +27682,7 @@
       <c r="S38" s="3"/>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A39" s="9">
+      <c r="A39" s="11">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
@@ -27696,7 +27712,7 @@
       <c r="S39" s="3"/>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A40" s="9">
+      <c r="A40" s="11">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
@@ -27726,7 +27742,7 @@
       <c r="S40" s="3"/>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A41" s="9">
+      <c r="A41" s="11">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
@@ -27756,7 +27772,7 @@
       <c r="S41" s="3"/>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A42" s="9">
+      <c r="A42" s="11">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
@@ -27786,7 +27802,7 @@
       <c r="S42" s="3"/>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A43" s="9">
+      <c r="A43" s="11">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
@@ -27816,7 +27832,7 @@
       <c r="S43" s="3"/>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A44" s="9">
+      <c r="A44" s="11">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
@@ -27846,7 +27862,7 @@
       <c r="S44" s="3"/>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A45" s="9">
+      <c r="A45" s="11">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
@@ -27876,7 +27892,7 @@
       <c r="S45" s="3"/>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A46" s="9">
+      <c r="A46" s="11">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
@@ -27906,7 +27922,7 @@
       <c r="S46" s="3"/>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A47" s="9">
+      <c r="A47" s="11">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
@@ -27936,7 +27952,7 @@
       <c r="S47" s="3"/>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A48" s="9">
+      <c r="A48" s="11">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
@@ -27966,7 +27982,7 @@
       <c r="S48" s="3"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="9">
+      <c r="A49" s="11">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
@@ -27996,7 +28012,7 @@
       <c r="S49" s="3"/>
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A50" s="9">
+      <c r="A50" s="11">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
@@ -28026,7 +28042,7 @@
       <c r="S50" s="3"/>
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A51" s="9">
+      <c r="A51" s="11">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
@@ -28056,7 +28072,7 @@
       <c r="S51" s="3"/>
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A52" s="9">
+      <c r="A52" s="11">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
@@ -28086,7 +28102,7 @@
       <c r="S52" s="3"/>
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A53" s="9">
+      <c r="A53" s="11">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
@@ -28116,7 +28132,7 @@
       <c r="S53" s="3"/>
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A54" s="9">
+      <c r="A54" s="11">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
@@ -28146,7 +28162,7 @@
       <c r="S54" s="3"/>
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A55" s="9">
+      <c r="A55" s="11">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
@@ -28176,7 +28192,7 @@
       <c r="S55" s="3"/>
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A56" s="9">
+      <c r="A56" s="11">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
@@ -28206,7 +28222,7 @@
       <c r="S56" s="3"/>
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A57" s="9">
+      <c r="A57" s="11">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
@@ -28236,7 +28252,7 @@
       <c r="S57" s="3"/>
     </row>
     <row r="58" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A58" s="9">
+      <c r="A58" s="11">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
@@ -28266,7 +28282,7 @@
       <c r="S58" s="3"/>
     </row>
     <row r="59" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A59" s="9">
+      <c r="A59" s="11">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
@@ -28296,7 +28312,7 @@
       <c r="S59" s="3"/>
     </row>
     <row r="60" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A60" s="9">
+      <c r="A60" s="11">
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
@@ -28326,7 +28342,7 @@
       <c r="S60" s="3"/>
     </row>
     <row r="61" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A61" s="9">
+      <c r="A61" s="11">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
@@ -28356,7 +28372,7 @@
       <c r="S61" s="3"/>
     </row>
     <row r="62" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A62" s="9">
+      <c r="A62" s="11">
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
@@ -28386,7 +28402,7 @@
       <c r="S62" s="3"/>
     </row>
     <row r="63" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A63" s="9">
+      <c r="A63" s="11">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
@@ -28416,7 +28432,7 @@
       <c r="S63" s="3"/>
     </row>
     <row r="64" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A64" s="9">
+      <c r="A64" s="11">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
@@ -28446,7 +28462,7 @@
       <c r="S64" s="3"/>
     </row>
     <row r="65" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A65" s="9">
+      <c r="A65" s="11">
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
@@ -28476,7 +28492,7 @@
       <c r="S65" s="3"/>
     </row>
     <row r="66" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A66" s="9">
+      <c r="A66" s="11">
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
@@ -28506,7 +28522,7 @@
       <c r="S66" s="3"/>
     </row>
     <row r="67" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A67" s="9">
+      <c r="A67" s="11">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
@@ -28536,7 +28552,7 @@
       <c r="S67" s="3"/>
     </row>
     <row r="68" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A68" s="9">
+      <c r="A68" s="11">
         <f t="shared" si="0"/>
         <v>65</v>
       </c>
@@ -28566,7 +28582,7 @@
       <c r="S68" s="3"/>
     </row>
     <row r="69" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A69" s="9">
+      <c r="A69" s="11">
         <f t="shared" si="0"/>
         <v>66</v>
       </c>
@@ -28596,7 +28612,7 @@
       <c r="S69" s="3"/>
     </row>
     <row r="70" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A70" s="9">
+      <c r="A70" s="11">
         <f t="shared" ref="A70:A133" si="1">1+A69</f>
         <v>67</v>
       </c>
@@ -28626,7 +28642,7 @@
       <c r="S70" s="3"/>
     </row>
     <row r="71" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A71" s="9">
+      <c r="A71" s="11">
         <f t="shared" si="1"/>
         <v>68</v>
       </c>
@@ -28656,7 +28672,7 @@
       <c r="S71" s="3"/>
     </row>
     <row r="72" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A72" s="9">
+      <c r="A72" s="11">
         <f t="shared" si="1"/>
         <v>69</v>
       </c>
@@ -28686,7 +28702,7 @@
       <c r="S72" s="3"/>
     </row>
     <row r="73" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A73" s="9">
+      <c r="A73" s="11">
         <f t="shared" si="1"/>
         <v>70</v>
       </c>
@@ -28716,7 +28732,7 @@
       <c r="S73" s="3"/>
     </row>
     <row r="74" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A74" s="9">
+      <c r="A74" s="11">
         <f t="shared" si="1"/>
         <v>71</v>
       </c>
@@ -28746,7 +28762,7 @@
       <c r="S74" s="3"/>
     </row>
     <row r="75" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A75" s="9">
+      <c r="A75" s="11">
         <f t="shared" si="1"/>
         <v>72</v>
       </c>
@@ -28776,7 +28792,7 @@
       <c r="S75" s="3"/>
     </row>
     <row r="76" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A76" s="9">
+      <c r="A76" s="11">
         <f t="shared" si="1"/>
         <v>73</v>
       </c>
@@ -28806,7 +28822,7 @@
       <c r="S76" s="3"/>
     </row>
     <row r="77" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A77" s="9">
+      <c r="A77" s="11">
         <f t="shared" si="1"/>
         <v>74</v>
       </c>
@@ -28836,7 +28852,7 @@
       <c r="S77" s="3"/>
     </row>
     <row r="78" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A78" s="9">
+      <c r="A78" s="11">
         <f t="shared" si="1"/>
         <v>75</v>
       </c>
@@ -28866,7 +28882,7 @@
       <c r="S78" s="3"/>
     </row>
     <row r="79" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A79" s="9">
+      <c r="A79" s="11">
         <f t="shared" si="1"/>
         <v>76</v>
       </c>
@@ -28896,7 +28912,7 @@
       <c r="S79" s="3"/>
     </row>
     <row r="80" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A80" s="9">
+      <c r="A80" s="11">
         <f t="shared" si="1"/>
         <v>77</v>
       </c>
@@ -28926,7 +28942,7 @@
       <c r="S80" s="3"/>
     </row>
     <row r="81" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A81" s="9">
+      <c r="A81" s="11">
         <f t="shared" si="1"/>
         <v>78</v>
       </c>
@@ -28956,7 +28972,7 @@
       <c r="S81" s="3"/>
     </row>
     <row r="82" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A82" s="9">
+      <c r="A82" s="11">
         <f t="shared" si="1"/>
         <v>79</v>
       </c>
@@ -28986,7 +29002,7 @@
       <c r="S82" s="3"/>
     </row>
     <row r="83" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A83" s="9">
+      <c r="A83" s="11">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
@@ -29016,7 +29032,7 @@
       <c r="S83" s="3"/>
     </row>
     <row r="84" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A84" s="9">
+      <c r="A84" s="11">
         <f t="shared" si="1"/>
         <v>81</v>
       </c>
@@ -29046,7 +29062,7 @@
       <c r="S84" s="3"/>
     </row>
     <row r="85" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A85" s="9">
+      <c r="A85" s="11">
         <f t="shared" si="1"/>
         <v>82</v>
       </c>
@@ -29076,7 +29092,7 @@
       <c r="S85" s="3"/>
     </row>
     <row r="86" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A86" s="9">
+      <c r="A86" s="11">
         <f t="shared" si="1"/>
         <v>83</v>
       </c>
@@ -29106,7 +29122,7 @@
       <c r="S86" s="3"/>
     </row>
     <row r="87" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A87" s="9">
+      <c r="A87" s="11">
         <f t="shared" si="1"/>
         <v>84</v>
       </c>
@@ -29136,7 +29152,7 @@
       <c r="S87" s="3"/>
     </row>
     <row r="88" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A88" s="9">
+      <c r="A88" s="11">
         <f t="shared" si="1"/>
         <v>85</v>
       </c>
@@ -29166,7 +29182,7 @@
       <c r="S88" s="3"/>
     </row>
     <row r="89" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A89" s="9">
+      <c r="A89" s="11">
         <f t="shared" si="1"/>
         <v>86</v>
       </c>
@@ -29196,7 +29212,7 @@
       <c r="S89" s="3"/>
     </row>
     <row r="90" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A90" s="9">
+      <c r="A90" s="11">
         <f t="shared" si="1"/>
         <v>87</v>
       </c>
@@ -29226,7 +29242,7 @@
       <c r="S90" s="3"/>
     </row>
     <row r="91" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A91" s="9">
+      <c r="A91" s="11">
         <f t="shared" si="1"/>
         <v>88</v>
       </c>
@@ -29256,7 +29272,7 @@
       <c r="S91" s="3"/>
     </row>
     <row r="92" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A92" s="9">
+      <c r="A92" s="11">
         <f t="shared" si="1"/>
         <v>89</v>
       </c>
@@ -29286,7 +29302,7 @@
       <c r="S92" s="3"/>
     </row>
     <row r="93" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A93" s="9">
+      <c r="A93" s="11">
         <f t="shared" si="1"/>
         <v>90</v>
       </c>
@@ -29316,7 +29332,7 @@
       <c r="S93" s="3"/>
     </row>
     <row r="94" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A94" s="9">
+      <c r="A94" s="11">
         <f t="shared" si="1"/>
         <v>91</v>
       </c>
@@ -29346,7 +29362,7 @@
       <c r="S94" s="3"/>
     </row>
     <row r="95" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A95" s="9">
+      <c r="A95" s="11">
         <f t="shared" si="1"/>
         <v>92</v>
       </c>
@@ -29376,7 +29392,7 @@
       <c r="S95" s="3"/>
     </row>
     <row r="96" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A96" s="9">
+      <c r="A96" s="11">
         <f t="shared" si="1"/>
         <v>93</v>
       </c>
@@ -29406,7 +29422,7 @@
       <c r="S96" s="3"/>
     </row>
     <row r="97" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A97" s="9">
+      <c r="A97" s="11">
         <f t="shared" si="1"/>
         <v>94</v>
       </c>
@@ -29436,7 +29452,7 @@
       <c r="S97" s="3"/>
     </row>
     <row r="98" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A98" s="9">
+      <c r="A98" s="11">
         <f t="shared" si="1"/>
         <v>95</v>
       </c>
@@ -29466,7 +29482,7 @@
       <c r="S98" s="3"/>
     </row>
     <row r="99" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A99" s="9">
+      <c r="A99" s="11">
         <f t="shared" si="1"/>
         <v>96</v>
       </c>
@@ -29496,7 +29512,7 @@
       <c r="S99" s="3"/>
     </row>
     <row r="100" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A100" s="9">
+      <c r="A100" s="11">
         <f t="shared" si="1"/>
         <v>97</v>
       </c>
@@ -29526,7 +29542,7 @@
       <c r="S100" s="3"/>
     </row>
     <row r="101" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A101" s="9">
+      <c r="A101" s="11">
         <f t="shared" si="1"/>
         <v>98</v>
       </c>
@@ -29556,7 +29572,7 @@
       <c r="S101" s="3"/>
     </row>
     <row r="102" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A102" s="9">
+      <c r="A102" s="11">
         <f t="shared" si="1"/>
         <v>99</v>
       </c>
@@ -29586,7 +29602,7 @@
       <c r="S102" s="3"/>
     </row>
     <row r="103" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A103" s="9">
+      <c r="A103" s="11">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
@@ -29616,7 +29632,7 @@
       <c r="S103" s="3"/>
     </row>
     <row r="104" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A104" s="9">
+      <c r="A104" s="11">
         <f t="shared" si="1"/>
         <v>101</v>
       </c>
@@ -29646,7 +29662,7 @@
       <c r="S104" s="3"/>
     </row>
     <row r="105" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A105" s="9">
+      <c r="A105" s="11">
         <f t="shared" si="1"/>
         <v>102</v>
       </c>
@@ -29676,7 +29692,7 @@
       <c r="S105" s="3"/>
     </row>
     <row r="106" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A106" s="9">
+      <c r="A106" s="11">
         <f t="shared" si="1"/>
         <v>103</v>
       </c>
@@ -29706,7 +29722,7 @@
       <c r="S106" s="3"/>
     </row>
     <row r="107" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A107" s="9">
+      <c r="A107" s="11">
         <f t="shared" si="1"/>
         <v>104</v>
       </c>
@@ -29736,7 +29752,7 @@
       <c r="S107" s="3"/>
     </row>
     <row r="108" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A108" s="9">
+      <c r="A108" s="11">
         <f t="shared" si="1"/>
         <v>105</v>
       </c>
@@ -29766,7 +29782,7 @@
       <c r="S108" s="3"/>
     </row>
     <row r="109" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A109" s="9">
+      <c r="A109" s="11">
         <f t="shared" si="1"/>
         <v>106</v>
       </c>
@@ -29796,7 +29812,7 @@
       <c r="S109" s="3"/>
     </row>
     <row r="110" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A110" s="9">
+      <c r="A110" s="11">
         <f t="shared" si="1"/>
         <v>107</v>
       </c>
@@ -29826,7 +29842,7 @@
       <c r="S110" s="3"/>
     </row>
     <row r="111" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A111" s="9">
+      <c r="A111" s="11">
         <f t="shared" si="1"/>
         <v>108</v>
       </c>
@@ -29856,7 +29872,7 @@
       <c r="S111" s="3"/>
     </row>
     <row r="112" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A112" s="9">
+      <c r="A112" s="11">
         <f t="shared" si="1"/>
         <v>109</v>
       </c>
@@ -29886,7 +29902,7 @@
       <c r="S112" s="3"/>
     </row>
     <row r="113" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A113" s="9">
+      <c r="A113" s="11">
         <f t="shared" si="1"/>
         <v>110</v>
       </c>
@@ -29916,7 +29932,7 @@
       <c r="S113" s="3"/>
     </row>
     <row r="114" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A114" s="9">
+      <c r="A114" s="11">
         <f t="shared" si="1"/>
         <v>111</v>
       </c>
@@ -29946,7 +29962,7 @@
       <c r="S114" s="3"/>
     </row>
     <row r="115" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A115" s="9">
+      <c r="A115" s="11">
         <f t="shared" si="1"/>
         <v>112</v>
       </c>
@@ -29976,7 +29992,7 @@
       <c r="S115" s="3"/>
     </row>
     <row r="116" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A116" s="9">
+      <c r="A116" s="11">
         <f t="shared" si="1"/>
         <v>113</v>
       </c>
@@ -30006,7 +30022,7 @@
       <c r="S116" s="3"/>
     </row>
     <row r="117" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A117" s="9">
+      <c r="A117" s="11">
         <f t="shared" si="1"/>
         <v>114</v>
       </c>
@@ -30032,7 +30048,7 @@
       <c r="S117" s="3"/>
     </row>
     <row r="118" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A118" s="9">
+      <c r="A118" s="11">
         <f t="shared" si="1"/>
         <v>115</v>
       </c>
@@ -30042,7 +30058,7 @@
       <c r="C118" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="D118" s="11"/>
+      <c r="D118" s="16"/>
       <c r="E118" s="3"/>
       <c r="F118" s="3"/>
       <c r="G118" s="3"/>
@@ -30060,7 +30076,7 @@
       <c r="S118" s="3"/>
     </row>
     <row r="119" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A119" s="9">
+      <c r="A119" s="11">
         <f t="shared" si="1"/>
         <v>116</v>
       </c>
@@ -30070,7 +30086,7 @@
       <c r="C119" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="D119" s="11"/>
+      <c r="D119" s="16"/>
       <c r="E119" s="3"/>
       <c r="F119" s="3"/>
       <c r="G119" s="3"/>
@@ -30088,7 +30104,7 @@
       <c r="S119" s="3"/>
     </row>
     <row r="120" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A120" s="9">
+      <c r="A120" s="11">
         <f t="shared" si="1"/>
         <v>117</v>
       </c>
@@ -30098,7 +30114,7 @@
       <c r="C120" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="D120" s="11"/>
+      <c r="D120" s="16"/>
       <c r="E120" s="3"/>
       <c r="F120" s="3"/>
       <c r="G120" s="3"/>
@@ -30116,7 +30132,7 @@
       <c r="S120" s="3"/>
     </row>
     <row r="121" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A121" s="9">
+      <c r="A121" s="11">
         <f t="shared" si="1"/>
         <v>118</v>
       </c>
@@ -30126,7 +30142,7 @@
       <c r="C121" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="D121" s="11"/>
+      <c r="D121" s="16"/>
       <c r="E121" s="3"/>
       <c r="F121" s="3"/>
       <c r="G121" s="3"/>
@@ -30144,7 +30160,7 @@
       <c r="S121" s="3"/>
     </row>
     <row r="122" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A122" s="9">
+      <c r="A122" s="11">
         <f t="shared" si="1"/>
         <v>119</v>
       </c>
@@ -30154,7 +30170,7 @@
       <c r="C122" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="D122" s="11"/>
+      <c r="D122" s="16"/>
       <c r="E122" s="3"/>
       <c r="F122" s="3"/>
       <c r="G122" s="3"/>
@@ -30172,7 +30188,7 @@
       <c r="S122" s="3"/>
     </row>
     <row r="123" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A123" s="9">
+      <c r="A123" s="11">
         <f t="shared" si="1"/>
         <v>120</v>
       </c>
@@ -30182,7 +30198,7 @@
       <c r="C123" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="D123" s="11"/>
+      <c r="D123" s="16"/>
       <c r="E123" s="3"/>
       <c r="F123" s="3"/>
       <c r="G123" s="3"/>
@@ -30200,7 +30216,7 @@
       <c r="S123" s="3"/>
     </row>
     <row r="124" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A124" s="9">
+      <c r="A124" s="11">
         <f t="shared" si="1"/>
         <v>121</v>
       </c>
@@ -30210,7 +30226,7 @@
       <c r="C124" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="D124" s="11"/>
+      <c r="D124" s="16"/>
       <c r="E124" s="3"/>
       <c r="F124" s="3"/>
       <c r="G124" s="3"/>
@@ -30228,7 +30244,7 @@
       <c r="S124" s="3"/>
     </row>
     <row r="125" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A125" s="9">
+      <c r="A125" s="11">
         <f t="shared" si="1"/>
         <v>122</v>
       </c>
@@ -30238,7 +30254,7 @@
       <c r="C125" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="D125" s="11"/>
+      <c r="D125" s="16"/>
       <c r="E125" s="3"/>
       <c r="F125" s="3"/>
       <c r="G125" s="3"/>
@@ -30256,7 +30272,7 @@
       <c r="S125" s="3"/>
     </row>
     <row r="126" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A126" s="9">
+      <c r="A126" s="11">
         <f t="shared" si="1"/>
         <v>123</v>
       </c>
@@ -30266,7 +30282,7 @@
       <c r="C126" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="D126" s="11"/>
+      <c r="D126" s="16"/>
       <c r="E126" s="3"/>
       <c r="F126" s="3"/>
       <c r="G126" s="3"/>
@@ -30284,7 +30300,7 @@
       <c r="S126" s="3"/>
     </row>
     <row r="127" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A127" s="9">
+      <c r="A127" s="11">
         <f t="shared" si="1"/>
         <v>124</v>
       </c>
@@ -30294,7 +30310,7 @@
       <c r="C127" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="D127" s="11"/>
+      <c r="D127" s="16"/>
       <c r="E127" s="3"/>
       <c r="F127" s="3"/>
       <c r="G127" s="3"/>
@@ -30312,7 +30328,7 @@
       <c r="S127" s="3"/>
     </row>
     <row r="128" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A128" s="9">
+      <c r="A128" s="11">
         <f t="shared" si="1"/>
         <v>125</v>
       </c>
@@ -30322,7 +30338,7 @@
       <c r="C128" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="D128" s="11"/>
+      <c r="D128" s="16"/>
       <c r="E128" s="3"/>
       <c r="F128" s="3"/>
       <c r="G128" s="3"/>
@@ -30340,7 +30356,7 @@
       <c r="S128" s="3"/>
     </row>
     <row r="129" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A129" s="9">
+      <c r="A129" s="11">
         <f t="shared" si="1"/>
         <v>126</v>
       </c>
@@ -30350,7 +30366,7 @@
       <c r="C129" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="D129" s="11"/>
+      <c r="D129" s="16"/>
       <c r="E129" s="3"/>
       <c r="F129" s="3"/>
       <c r="G129" s="3"/>
@@ -30368,7 +30384,7 @@
       <c r="S129" s="3"/>
     </row>
     <row r="130" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A130" s="9">
+      <c r="A130" s="11">
         <f t="shared" si="1"/>
         <v>127</v>
       </c>
@@ -30378,7 +30394,7 @@
       <c r="C130" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="D130" s="11"/>
+      <c r="D130" s="16"/>
       <c r="E130" s="3"/>
       <c r="F130" s="3"/>
       <c r="G130" s="3"/>
@@ -30396,7 +30412,7 @@
       <c r="S130" s="3"/>
     </row>
     <row r="131" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A131" s="9">
+      <c r="A131" s="11">
         <f t="shared" si="1"/>
         <v>128</v>
       </c>
@@ -30406,7 +30422,7 @@
       <c r="C131" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="D131" s="11"/>
+      <c r="D131" s="16"/>
       <c r="E131" s="3"/>
       <c r="F131" s="3"/>
       <c r="G131" s="3"/>
@@ -30424,7 +30440,7 @@
       <c r="S131" s="3"/>
     </row>
     <row r="132" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A132" s="9">
+      <c r="A132" s="11">
         <f t="shared" si="1"/>
         <v>129</v>
       </c>
@@ -30434,7 +30450,7 @@
       <c r="C132" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="D132" s="11"/>
+      <c r="D132" s="16"/>
       <c r="E132" s="3"/>
       <c r="F132" s="3"/>
       <c r="G132" s="3"/>
@@ -30452,7 +30468,7 @@
       <c r="S132" s="3"/>
     </row>
     <row r="133" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A133" s="9">
+      <c r="A133" s="11">
         <f t="shared" si="1"/>
         <v>130</v>
       </c>
@@ -30462,7 +30478,7 @@
       <c r="C133" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="D133" s="11"/>
+      <c r="D133" s="16"/>
       <c r="E133" s="3"/>
       <c r="F133" s="3"/>
       <c r="G133" s="3"/>
@@ -30480,7 +30496,7 @@
       <c r="S133" s="3"/>
     </row>
     <row r="134" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A134" s="9">
+      <c r="A134" s="11">
         <f t="shared" ref="A134:A197" si="2">1+A133</f>
         <v>131</v>
       </c>
@@ -30490,7 +30506,7 @@
       <c r="C134" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="D134" s="11"/>
+      <c r="D134" s="16"/>
       <c r="E134" s="3"/>
       <c r="F134" s="3"/>
       <c r="G134" s="3"/>
@@ -30508,7 +30524,7 @@
       <c r="S134" s="3"/>
     </row>
     <row r="135" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A135" s="9">
+      <c r="A135" s="11">
         <f t="shared" si="2"/>
         <v>132</v>
       </c>
@@ -30518,7 +30534,7 @@
       <c r="C135" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="D135" s="11"/>
+      <c r="D135" s="16"/>
       <c r="E135" s="3"/>
       <c r="F135" s="3"/>
       <c r="G135" s="3"/>
@@ -30536,7 +30552,7 @@
       <c r="S135" s="3"/>
     </row>
     <row r="136" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A136" s="9">
+      <c r="A136" s="11">
         <f t="shared" si="2"/>
         <v>133</v>
       </c>
@@ -30562,7 +30578,7 @@
       <c r="S136" s="3"/>
     </row>
     <row r="137" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A137" s="9">
+      <c r="A137" s="11">
         <f t="shared" si="2"/>
         <v>134</v>
       </c>
@@ -30572,7 +30588,7 @@
       <c r="C137" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="D137" s="11">
+      <c r="D137" s="16">
         <v>1028470016</v>
       </c>
       <c r="E137" s="3"/>
@@ -30592,7 +30608,7 @@
       <c r="S137" s="3"/>
     </row>
     <row r="138" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A138" s="9">
+      <c r="A138" s="11">
         <f t="shared" si="2"/>
         <v>135</v>
       </c>
@@ -30602,7 +30618,7 @@
       <c r="C138" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="D138" s="11">
+      <c r="D138" s="16">
         <v>1022370544</v>
       </c>
       <c r="E138" s="3"/>
@@ -30622,7 +30638,7 @@
       <c r="S138" s="3"/>
     </row>
     <row r="139" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A139" s="9">
+      <c r="A139" s="11">
         <f t="shared" si="2"/>
         <v>136</v>
       </c>
@@ -30632,7 +30648,7 @@
       <c r="C139" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="D139" s="11">
+      <c r="D139" s="16">
         <v>1021736512</v>
       </c>
       <c r="E139" s="3"/>
@@ -30652,7 +30668,7 @@
       <c r="S139" s="3"/>
     </row>
     <row r="140" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A140" s="9">
+      <c r="A140" s="11">
         <f t="shared" si="2"/>
         <v>137</v>
       </c>
@@ -30662,7 +30678,7 @@
       <c r="C140" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="D140" s="11">
+      <c r="D140" s="16">
         <v>963349356</v>
       </c>
       <c r="E140" s="3"/>
@@ -30682,7 +30698,7 @@
       <c r="S140" s="3"/>
     </row>
     <row r="141" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A141" s="9">
+      <c r="A141" s="11">
         <f t="shared" si="2"/>
         <v>138</v>
       </c>
@@ -30692,7 +30708,7 @@
       <c r="C141" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="D141" s="11">
+      <c r="D141" s="16">
         <v>916057056</v>
       </c>
       <c r="E141" s="3"/>
@@ -30712,7 +30728,7 @@
       <c r="S141" s="3"/>
     </row>
     <row r="142" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A142" s="9">
+      <c r="A142" s="11">
         <f t="shared" si="2"/>
         <v>139</v>
       </c>
@@ -30722,7 +30738,7 @@
       <c r="C142" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="D142" s="11">
+      <c r="D142" s="16">
         <v>915770679</v>
       </c>
       <c r="E142" s="3"/>
@@ -30742,7 +30758,7 @@
       <c r="S142" s="3"/>
     </row>
     <row r="143" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A143" s="9">
+      <c r="A143" s="11">
         <f t="shared" si="2"/>
         <v>140</v>
       </c>
@@ -30752,7 +30768,7 @@
       <c r="C143" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="D143" s="11">
+      <c r="D143" s="16">
         <v>897741791</v>
       </c>
       <c r="E143" s="3"/>
@@ -30772,7 +30788,7 @@
       <c r="S143" s="3"/>
     </row>
     <row r="144" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A144" s="9">
+      <c r="A144" s="11">
         <f t="shared" si="2"/>
         <v>141</v>
       </c>
@@ -30782,7 +30798,7 @@
       <c r="C144" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="D144" s="11">
+      <c r="D144" s="16">
         <v>883459968</v>
       </c>
       <c r="E144" s="3"/>
@@ -30802,7 +30818,7 @@
       <c r="S144" s="3"/>
     </row>
     <row r="145" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A145" s="9">
+      <c r="A145" s="11">
         <f t="shared" si="2"/>
         <v>142</v>
       </c>
@@ -30812,7 +30828,7 @@
       <c r="C145" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="D145" s="11">
+      <c r="D145" s="16">
         <v>879114752</v>
       </c>
       <c r="E145" s="3"/>
@@ -30832,7 +30848,7 @@
       <c r="S145" s="3"/>
     </row>
     <row r="146" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A146" s="9">
+      <c r="A146" s="11">
         <f t="shared" si="2"/>
         <v>143</v>
       </c>
@@ -30842,7 +30858,7 @@
       <c r="C146" s="3" t="s">
         <v>369</v>
       </c>
-      <c r="D146" s="11">
+      <c r="D146" s="16">
         <v>872812480</v>
       </c>
       <c r="E146" s="3"/>
@@ -30862,7 +30878,7 @@
       <c r="S146" s="3"/>
     </row>
     <row r="147" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A147" s="9">
+      <c r="A147" s="11">
         <f t="shared" si="2"/>
         <v>144</v>
       </c>
@@ -30872,7 +30888,7 @@
       <c r="C147" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="D147" s="11">
+      <c r="D147" s="16">
         <v>867636904</v>
       </c>
       <c r="E147" s="3"/>
@@ -30892,7 +30908,7 @@
       <c r="S147" s="3"/>
     </row>
     <row r="148" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A148" s="9">
+      <c r="A148" s="11">
         <f t="shared" si="2"/>
         <v>145</v>
       </c>
@@ -30902,7 +30918,7 @@
       <c r="C148" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="D148" s="11">
+      <c r="D148" s="16">
         <v>839963968</v>
       </c>
       <c r="E148" s="3"/>
@@ -30922,7 +30938,7 @@
       <c r="S148" s="3"/>
     </row>
     <row r="149" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A149" s="9">
+      <c r="A149" s="11">
         <f t="shared" si="2"/>
         <v>146</v>
       </c>
@@ -30932,7 +30948,7 @@
       <c r="C149" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="D149" s="11">
+      <c r="D149" s="16">
         <v>809358135</v>
       </c>
       <c r="E149" s="3"/>
@@ -30952,7 +30968,7 @@
       <c r="S149" s="3"/>
     </row>
     <row r="150" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A150" s="9">
+      <c r="A150" s="11">
         <f t="shared" si="2"/>
         <v>147</v>
       </c>
@@ -30962,7 +30978,7 @@
       <c r="C150" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="D150" s="11">
+      <c r="D150" s="16">
         <v>806839340</v>
       </c>
       <c r="E150" s="3"/>
@@ -30982,7 +30998,7 @@
       <c r="S150" s="3"/>
     </row>
     <row r="151" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A151" s="9">
+      <c r="A151" s="11">
         <f t="shared" si="2"/>
         <v>148</v>
       </c>
@@ -30992,7 +31008,7 @@
       <c r="C151" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="D151" s="11">
+      <c r="D151" s="16">
         <v>804490880</v>
       </c>
       <c r="E151" s="3"/>
@@ -31012,7 +31028,7 @@
       <c r="S151" s="3"/>
     </row>
     <row r="152" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A152" s="9">
+      <c r="A152" s="11">
         <f t="shared" si="2"/>
         <v>149</v>
       </c>
@@ -31022,7 +31038,7 @@
       <c r="C152" s="3" t="s">
         <v>381</v>
       </c>
-      <c r="D152" s="11">
+      <c r="D152" s="16">
         <v>796813376</v>
       </c>
       <c r="E152" s="3"/>
@@ -31042,7 +31058,7 @@
       <c r="S152" s="3"/>
     </row>
     <row r="153" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A153" s="9">
+      <c r="A153" s="11">
         <f t="shared" si="2"/>
         <v>150</v>
       </c>
@@ -31052,7 +31068,7 @@
       <c r="C153" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="D153" s="11">
+      <c r="D153" s="16">
         <v>791724160</v>
       </c>
       <c r="E153" s="3"/>
@@ -31072,7 +31088,7 @@
       <c r="S153" s="3"/>
     </row>
     <row r="154" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A154" s="9">
+      <c r="A154" s="11">
         <f t="shared" si="2"/>
         <v>151</v>
       </c>
@@ -31082,7 +31098,7 @@
       <c r="C154" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="D154" s="11">
+      <c r="D154" s="16">
         <v>781390144</v>
       </c>
       <c r="E154" s="3"/>
@@ -31102,7 +31118,7 @@
       <c r="S154" s="3"/>
     </row>
     <row r="155" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A155" s="9">
+      <c r="A155" s="11">
         <f t="shared" si="2"/>
         <v>152</v>
       </c>
@@ -31112,7 +31128,7 @@
       <c r="C155" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="D155" s="11">
+      <c r="D155" s="16">
         <v>771114578</v>
       </c>
       <c r="E155" s="3"/>
@@ -31132,7 +31148,7 @@
       <c r="S155" s="3"/>
     </row>
     <row r="156" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A156" s="9">
+      <c r="A156" s="11">
         <f t="shared" si="2"/>
         <v>153</v>
       </c>
@@ -31142,7 +31158,7 @@
       <c r="C156" s="3" t="s">
         <v>389</v>
       </c>
-      <c r="D156" s="11">
+      <c r="D156" s="16">
         <v>724678791</v>
       </c>
       <c r="E156" s="3"/>
@@ -31162,7 +31178,7 @@
       <c r="S156" s="3"/>
     </row>
     <row r="157" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A157" s="9">
+      <c r="A157" s="11">
         <f t="shared" si="2"/>
         <v>154</v>
       </c>
@@ -31172,7 +31188,7 @@
       <c r="C157" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="D157" s="11">
+      <c r="D157" s="16">
         <v>718399128</v>
       </c>
       <c r="E157" s="3"/>
@@ -31192,7 +31208,7 @@
       <c r="S157" s="3"/>
     </row>
     <row r="158" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A158" s="9">
+      <c r="A158" s="11">
         <f t="shared" si="2"/>
         <v>155</v>
       </c>
@@ -31202,7 +31218,7 @@
       <c r="C158" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="D158" s="11">
+      <c r="D158" s="16">
         <v>683822012</v>
       </c>
       <c r="E158" s="3"/>
@@ -31222,7 +31238,7 @@
       <c r="S158" s="3"/>
     </row>
     <row r="159" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A159" s="9">
+      <c r="A159" s="11">
         <f t="shared" si="2"/>
         <v>156</v>
       </c>
@@ -31232,7 +31248,7 @@
       <c r="C159" s="3" t="s">
         <v>395</v>
       </c>
-      <c r="D159" s="11">
+      <c r="D159" s="16">
         <v>680072870</v>
       </c>
       <c r="E159" s="3"/>
@@ -31252,7 +31268,7 @@
       <c r="S159" s="3"/>
     </row>
     <row r="160" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A160" s="9">
+      <c r="A160" s="11">
         <f t="shared" si="2"/>
         <v>157</v>
       </c>
@@ -31262,7 +31278,7 @@
       <c r="C160" s="3" t="s">
         <v>397</v>
       </c>
-      <c r="D160" s="11">
+      <c r="D160" s="16">
         <v>670485458</v>
       </c>
       <c r="E160" s="3"/>
@@ -31282,7 +31298,7 @@
       <c r="S160" s="3"/>
     </row>
     <row r="161" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A161" s="9">
+      <c r="A161" s="11">
         <f t="shared" si="2"/>
         <v>158</v>
       </c>
@@ -31292,7 +31308,7 @@
       <c r="C161" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="D161" s="11">
+      <c r="D161" s="16">
         <v>662825024</v>
       </c>
       <c r="E161" s="3"/>
@@ -31312,7 +31328,7 @@
       <c r="S161" s="3"/>
     </row>
     <row r="162" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A162" s="9">
+      <c r="A162" s="11">
         <f t="shared" si="2"/>
         <v>159</v>
       </c>
@@ -31322,7 +31338,7 @@
       <c r="C162" s="3" t="s">
         <v>401</v>
       </c>
-      <c r="D162" s="11">
+      <c r="D162" s="16">
         <v>632421708</v>
       </c>
       <c r="E162" s="3"/>
@@ -31342,7 +31358,7 @@
       <c r="S162" s="3"/>
     </row>
     <row r="163" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A163" s="9">
+      <c r="A163" s="11">
         <f t="shared" si="2"/>
         <v>160</v>
       </c>
@@ -31352,7 +31368,7 @@
       <c r="C163" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="D163" s="11">
+      <c r="D163" s="16">
         <v>623013781</v>
       </c>
       <c r="E163" s="3"/>
@@ -31372,7 +31388,7 @@
       <c r="S163" s="3"/>
     </row>
     <row r="164" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A164" s="9">
+      <c r="A164" s="11">
         <f t="shared" si="2"/>
         <v>161</v>
       </c>
@@ -31382,7 +31398,7 @@
       <c r="C164" s="3" t="s">
         <v>405</v>
       </c>
-      <c r="D164" s="11">
+      <c r="D164" s="16">
         <v>618756316</v>
       </c>
       <c r="E164" s="3"/>
@@ -31402,7 +31418,7 @@
       <c r="S164" s="3"/>
     </row>
     <row r="165" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A165" s="9">
+      <c r="A165" s="11">
         <f t="shared" si="2"/>
         <v>162</v>
       </c>
@@ -31412,7 +31428,7 @@
       <c r="C165" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="D165" s="11">
+      <c r="D165" s="16">
         <v>605217437</v>
       </c>
       <c r="E165" s="3"/>
@@ -31432,7 +31448,7 @@
       <c r="S165" s="3"/>
     </row>
     <row r="166" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A166" s="9">
+      <c r="A166" s="11">
         <f t="shared" si="2"/>
         <v>163</v>
       </c>
@@ -31442,7 +31458,7 @@
       <c r="C166" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="D166" s="11">
+      <c r="D166" s="16">
         <v>603712925</v>
       </c>
       <c r="E166" s="3"/>
@@ -31462,7 +31478,7 @@
       <c r="S166" s="3"/>
     </row>
     <row r="167" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A167" s="9">
+      <c r="A167" s="11">
         <f t="shared" si="2"/>
         <v>164</v>
       </c>
@@ -31472,7 +31488,7 @@
       <c r="C167" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="D167" s="11">
+      <c r="D167" s="16">
         <v>597003776</v>
       </c>
       <c r="E167" s="3"/>
@@ -31492,7 +31508,7 @@
       <c r="S167" s="3"/>
     </row>
     <row r="168" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A168" s="9">
+      <c r="A168" s="11">
         <f t="shared" si="2"/>
         <v>165</v>
       </c>
@@ -31502,7 +31518,7 @@
       <c r="C168" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="D168" s="11">
+      <c r="D168" s="16">
         <v>584677952</v>
       </c>
       <c r="E168" s="3"/>
@@ -31522,7 +31538,7 @@
       <c r="S168" s="3"/>
     </row>
     <row r="169" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A169" s="9">
+      <c r="A169" s="11">
         <f t="shared" si="2"/>
         <v>166</v>
       </c>
@@ -31532,7 +31548,7 @@
       <c r="C169" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="D169" s="11">
+      <c r="D169" s="16">
         <v>566445210</v>
       </c>
       <c r="E169" s="3"/>
@@ -31552,7 +31568,7 @@
       <c r="S169" s="3"/>
     </row>
     <row r="170" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A170" s="9">
+      <c r="A170" s="11">
         <f t="shared" si="2"/>
         <v>167</v>
       </c>
@@ -31562,7 +31578,7 @@
       <c r="C170" s="3" t="s">
         <v>417</v>
       </c>
-      <c r="D170" s="11">
+      <c r="D170" s="16">
         <v>553275584</v>
       </c>
       <c r="E170" s="3"/>
@@ -31582,7 +31598,7 @@
       <c r="S170" s="3"/>
     </row>
     <row r="171" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A171" s="9">
+      <c r="A171" s="11">
         <f t="shared" si="2"/>
         <v>168</v>
       </c>
@@ -31592,7 +31608,7 @@
       <c r="C171" s="3" t="s">
         <v>419</v>
       </c>
-      <c r="D171" s="11">
+      <c r="D171" s="16">
         <v>551565170</v>
       </c>
       <c r="E171" s="3"/>
@@ -31612,7 +31628,7 @@
       <c r="S171" s="3"/>
     </row>
     <row r="172" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A172" s="9">
+      <c r="A172" s="11">
         <f t="shared" si="2"/>
         <v>169</v>
       </c>
@@ -31622,7 +31638,7 @@
       <c r="C172" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="D172" s="11">
+      <c r="D172" s="16">
         <v>532741248</v>
       </c>
       <c r="E172" s="3"/>
@@ -31642,7 +31658,7 @@
       <c r="S172" s="3"/>
     </row>
     <row r="173" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A173" s="9">
+      <c r="A173" s="11">
         <f t="shared" si="2"/>
         <v>170</v>
       </c>
@@ -31652,7 +31668,7 @@
       <c r="C173" s="3" t="s">
         <v>423</v>
       </c>
-      <c r="D173" s="11">
+      <c r="D173" s="16">
         <v>528815488</v>
       </c>
       <c r="E173" s="3"/>
@@ -31672,7 +31688,7 @@
       <c r="S173" s="3"/>
     </row>
     <row r="174" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A174" s="9">
+      <c r="A174" s="11">
         <f t="shared" si="2"/>
         <v>171</v>
       </c>
@@ -31682,7 +31698,7 @@
       <c r="C174" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="D174" s="11">
+      <c r="D174" s="16">
         <v>505292285</v>
       </c>
       <c r="E174" s="3"/>
@@ -31702,7 +31718,7 @@
       <c r="S174" s="3"/>
     </row>
     <row r="175" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A175" s="9">
+      <c r="A175" s="11">
         <f t="shared" si="2"/>
         <v>172</v>
       </c>
@@ -31712,7 +31728,7 @@
       <c r="C175" s="3" t="s">
         <v>427</v>
       </c>
-      <c r="D175" s="11">
+      <c r="D175" s="16">
         <v>496141728</v>
       </c>
       <c r="E175" s="3"/>
@@ -31732,7 +31748,7 @@
       <c r="S175" s="3"/>
     </row>
     <row r="176" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A176" s="9">
+      <c r="A176" s="11">
         <f t="shared" si="2"/>
         <v>173</v>
       </c>
@@ -31742,7 +31758,7 @@
       <c r="C176" s="3" t="s">
         <v>429</v>
       </c>
-      <c r="D176" s="11">
+      <c r="D176" s="16">
         <v>485312008</v>
       </c>
       <c r="E176" s="3"/>
@@ -31762,7 +31778,7 @@
       <c r="S176" s="3"/>
     </row>
     <row r="177" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A177" s="9">
+      <c r="A177" s="11">
         <f t="shared" si="2"/>
         <v>174</v>
       </c>
@@ -31772,7 +31788,7 @@
       <c r="C177" s="3" t="s">
         <v>431</v>
       </c>
-      <c r="D177" s="11">
+      <c r="D177" s="16">
         <v>466570608</v>
       </c>
       <c r="E177" s="3"/>
@@ -31792,7 +31808,7 @@
       <c r="S177" s="3"/>
     </row>
     <row r="178" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A178" s="9">
+      <c r="A178" s="11">
         <f t="shared" si="2"/>
         <v>175</v>
       </c>
@@ -31802,7 +31818,7 @@
       <c r="C178" s="3" t="s">
         <v>433</v>
       </c>
-      <c r="D178" s="11">
+      <c r="D178" s="16">
         <v>461955072</v>
       </c>
       <c r="E178" s="3"/>
@@ -31822,7 +31838,7 @@
       <c r="S178" s="3"/>
     </row>
     <row r="179" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A179" s="9">
+      <c r="A179" s="11">
         <f t="shared" si="2"/>
         <v>176</v>
       </c>
@@ -31832,7 +31848,7 @@
       <c r="C179" s="3" t="s">
         <v>435</v>
       </c>
-      <c r="D179" s="11">
+      <c r="D179" s="16">
         <v>430596743</v>
       </c>
       <c r="E179" s="3"/>
@@ -31852,7 +31868,7 @@
       <c r="S179" s="3"/>
     </row>
     <row r="180" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A180" s="9">
+      <c r="A180" s="11">
         <f t="shared" si="2"/>
         <v>177</v>
       </c>
@@ -31862,7 +31878,7 @@
       <c r="C180" s="3" t="s">
         <v>437</v>
       </c>
-      <c r="D180" s="11">
+      <c r="D180" s="16">
         <v>425832064</v>
       </c>
       <c r="E180" s="3"/>
@@ -31882,7 +31898,7 @@
       <c r="S180" s="3"/>
     </row>
     <row r="181" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A181" s="9">
+      <c r="A181" s="11">
         <f t="shared" si="2"/>
         <v>178</v>
       </c>
@@ -31892,7 +31908,7 @@
       <c r="C181" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="D181" s="11">
+      <c r="D181" s="16">
         <v>422887239</v>
       </c>
       <c r="E181" s="3"/>
@@ -31912,7 +31928,7 @@
       <c r="S181" s="3"/>
     </row>
     <row r="182" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A182" s="9">
+      <c r="A182" s="11">
         <f t="shared" si="2"/>
         <v>179</v>
       </c>
@@ -31922,7 +31938,7 @@
       <c r="C182" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="D182" s="11">
+      <c r="D182" s="16">
         <v>411193379</v>
       </c>
       <c r="E182" s="3"/>
@@ -31942,7 +31958,7 @@
       <c r="S182" s="3"/>
     </row>
     <row r="183" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A183" s="9">
+      <c r="A183" s="11">
         <f t="shared" si="2"/>
         <v>180</v>
       </c>
@@ -31952,7 +31968,7 @@
       <c r="C183" s="3" t="s">
         <v>443</v>
       </c>
-      <c r="D183" s="11">
+      <c r="D183" s="16">
         <v>408410272</v>
       </c>
       <c r="E183" s="3"/>
@@ -31972,7 +31988,7 @@
       <c r="S183" s="3"/>
     </row>
     <row r="184" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A184" s="9">
+      <c r="A184" s="11">
         <f t="shared" si="2"/>
         <v>181</v>
       </c>
@@ -31982,7 +31998,7 @@
       <c r="C184" s="3" t="s">
         <v>445</v>
       </c>
-      <c r="D184" s="11">
+      <c r="D184" s="16">
         <v>408284160</v>
       </c>
       <c r="E184" s="3"/>
@@ -32002,7 +32018,7 @@
       <c r="S184" s="3"/>
     </row>
     <row r="185" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A185" s="9">
+      <c r="A185" s="11">
         <f t="shared" si="2"/>
         <v>182</v>
       </c>
@@ -32012,7 +32028,7 @@
       <c r="C185" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="D185" s="11">
+      <c r="D185" s="16">
         <v>353468063</v>
       </c>
       <c r="E185" s="3"/>
@@ -32032,7 +32048,7 @@
       <c r="S185" s="3"/>
     </row>
     <row r="186" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A186" s="9">
+      <c r="A186" s="11">
         <f t="shared" si="2"/>
         <v>183</v>
       </c>
@@ -32042,7 +32058,7 @@
       <c r="C186" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="D186" s="11">
+      <c r="D186" s="16">
         <v>349247553</v>
       </c>
       <c r="E186" s="3"/>
@@ -32062,7 +32078,7 @@
       <c r="S186" s="3"/>
     </row>
     <row r="187" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A187" s="9">
+      <c r="A187" s="11">
         <f t="shared" si="2"/>
         <v>184</v>
       </c>
@@ -32072,7 +32088,7 @@
       <c r="C187" s="3" t="s">
         <v>451</v>
       </c>
-      <c r="D187" s="11">
+      <c r="D187" s="16">
         <v>345361752</v>
       </c>
       <c r="E187" s="3"/>
@@ -32092,7 +32108,7 @@
       <c r="S187" s="3"/>
     </row>
     <row r="188" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A188" s="9">
+      <c r="A188" s="11">
         <f t="shared" si="2"/>
         <v>185</v>
       </c>
@@ -32102,7 +32118,7 @@
       <c r="C188" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="D188" s="11">
+      <c r="D188" s="16">
         <v>331858169</v>
       </c>
       <c r="E188" s="3"/>
@@ -32122,7 +32138,7 @@
       <c r="S188" s="3"/>
     </row>
     <row r="189" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A189" s="9">
+      <c r="A189" s="11">
         <f t="shared" si="2"/>
         <v>186</v>
       </c>
@@ -32132,7 +32148,7 @@
       <c r="C189" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="D189" s="11">
+      <c r="D189" s="16">
         <v>329036001</v>
       </c>
       <c r="E189" s="3"/>
@@ -32152,7 +32168,7 @@
       <c r="S189" s="3"/>
     </row>
     <row r="190" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A190" s="9">
+      <c r="A190" s="11">
         <f t="shared" si="2"/>
         <v>187</v>
       </c>
@@ -32162,7 +32178,7 @@
       <c r="C190" s="3" t="s">
         <v>457</v>
       </c>
-      <c r="D190" s="11">
+      <c r="D190" s="16">
         <v>321877568</v>
       </c>
       <c r="E190" s="3"/>
@@ -32182,7 +32198,7 @@
       <c r="S190" s="3"/>
     </row>
     <row r="191" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A191" s="9">
+      <c r="A191" s="11">
         <f t="shared" si="2"/>
         <v>188</v>
       </c>
@@ -32192,7 +32208,7 @@
       <c r="C191" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="D191" s="11">
+      <c r="D191" s="16">
         <v>313822272</v>
       </c>
       <c r="E191" s="3"/>
@@ -32212,7 +32228,7 @@
       <c r="S191" s="3"/>
     </row>
     <row r="192" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A192" s="9">
+      <c r="A192" s="11">
         <f t="shared" si="2"/>
         <v>189</v>
       </c>
@@ -32222,7 +32238,7 @@
       <c r="C192" s="3" t="s">
         <v>461</v>
       </c>
-      <c r="D192" s="11">
+      <c r="D192" s="16">
         <v>313733984</v>
       </c>
       <c r="E192" s="3"/>
@@ -32242,7 +32258,7 @@
       <c r="S192" s="3"/>
     </row>
     <row r="193" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A193" s="9">
+      <c r="A193" s="11">
         <f t="shared" si="2"/>
         <v>190</v>
       </c>
@@ -32252,7 +32268,7 @@
       <c r="C193" s="3" t="s">
         <v>463</v>
       </c>
-      <c r="D193" s="11">
+      <c r="D193" s="16">
         <v>309899296</v>
       </c>
       <c r="E193" s="3"/>
@@ -32272,7 +32288,7 @@
       <c r="S193" s="3"/>
     </row>
     <row r="194" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A194" s="9">
+      <c r="A194" s="11">
         <f t="shared" si="2"/>
         <v>191</v>
       </c>
@@ -32282,7 +32298,7 @@
       <c r="C194" s="3" t="s">
         <v>465</v>
       </c>
-      <c r="D194" s="11">
+      <c r="D194" s="16">
         <v>300329354</v>
       </c>
       <c r="E194" s="3"/>
@@ -32302,7 +32318,7 @@
       <c r="S194" s="3"/>
     </row>
     <row r="195" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A195" s="9">
+      <c r="A195" s="11">
         <f t="shared" si="2"/>
         <v>192</v>
       </c>
@@ -32312,7 +32328,7 @@
       <c r="C195" s="3" t="s">
         <v>467</v>
       </c>
-      <c r="D195" s="11">
+      <c r="D195" s="16">
         <v>292311584</v>
       </c>
       <c r="E195" s="3"/>
@@ -32332,7 +32348,7 @@
       <c r="S195" s="3"/>
     </row>
     <row r="196" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A196" s="9">
+      <c r="A196" s="11">
         <f t="shared" si="2"/>
         <v>193</v>
       </c>
@@ -32342,7 +32358,7 @@
       <c r="C196" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="D196" s="11">
+      <c r="D196" s="16">
         <v>279334304</v>
       </c>
       <c r="E196" s="3"/>
@@ -32362,7 +32378,7 @@
       <c r="S196" s="3"/>
     </row>
     <row r="197" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A197" s="9">
+      <c r="A197" s="11">
         <f t="shared" si="2"/>
         <v>194</v>
       </c>
@@ -32372,7 +32388,7 @@
       <c r="C197" s="3" t="s">
         <v>471</v>
       </c>
-      <c r="D197" s="11">
+      <c r="D197" s="16">
         <v>276176433</v>
       </c>
       <c r="E197" s="3"/>
@@ -32392,7 +32408,7 @@
       <c r="S197" s="3"/>
     </row>
     <row r="198" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A198" s="9">
+      <c r="A198" s="11">
         <f t="shared" ref="A198:A261" si="3">1+A197</f>
         <v>195</v>
       </c>
@@ -32402,7 +32418,7 @@
       <c r="C198" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="D198" s="11">
+      <c r="D198" s="16">
         <v>273508640</v>
       </c>
       <c r="E198" s="3"/>
@@ -32422,7 +32438,7 @@
       <c r="S198" s="3"/>
     </row>
     <row r="199" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A199" s="9">
+      <c r="A199" s="11">
         <f t="shared" si="3"/>
         <v>196</v>
       </c>
@@ -32432,7 +32448,7 @@
       <c r="C199" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="D199" s="11">
+      <c r="D199" s="16">
         <v>272816752</v>
       </c>
       <c r="E199" s="3"/>
@@ -32452,7 +32468,7 @@
       <c r="S199" s="3"/>
     </row>
     <row r="200" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A200" s="9">
+      <c r="A200" s="11">
         <f t="shared" si="3"/>
         <v>197</v>
       </c>
@@ -32462,7 +32478,7 @@
       <c r="C200" s="3" t="s">
         <v>477</v>
       </c>
-      <c r="D200" s="11">
+      <c r="D200" s="16">
         <v>261084442</v>
       </c>
       <c r="E200" s="3"/>
@@ -32482,7 +32498,7 @@
       <c r="S200" s="3"/>
     </row>
     <row r="201" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A201" s="9">
+      <c r="A201" s="11">
         <f t="shared" si="3"/>
         <v>198</v>
       </c>
@@ -32492,7 +32508,7 @@
       <c r="C201" s="3" t="s">
         <v>479</v>
       </c>
-      <c r="D201" s="11">
+      <c r="D201" s="16">
         <v>250590912</v>
       </c>
       <c r="E201" s="3"/>
@@ -32512,7 +32528,7 @@
       <c r="S201" s="3"/>
     </row>
     <row r="202" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A202" s="9">
+      <c r="A202" s="11">
         <f t="shared" si="3"/>
         <v>199</v>
       </c>
@@ -32522,7 +32538,7 @@
       <c r="C202" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="D202" s="11">
+      <c r="D202" s="16">
         <v>248981418</v>
       </c>
       <c r="E202" s="3"/>
@@ -32542,7 +32558,7 @@
       <c r="S202" s="3"/>
     </row>
     <row r="203" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A203" s="9">
+      <c r="A203" s="11">
         <f t="shared" si="3"/>
         <v>200</v>
       </c>
@@ -32568,7 +32584,7 @@
       <c r="S203" s="3"/>
     </row>
     <row r="204" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A204" s="9">
+      <c r="A204" s="11">
         <f t="shared" si="3"/>
         <v>201</v>
       </c>
@@ -32578,7 +32594,7 @@
       <c r="C204" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="D204" s="11">
+      <c r="D204" s="16">
         <v>243907047</v>
       </c>
       <c r="E204" s="3"/>
@@ -32598,7 +32614,7 @@
       <c r="S204" s="3"/>
     </row>
     <row r="205" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A205" s="9">
+      <c r="A205" s="11">
         <f t="shared" si="3"/>
         <v>202</v>
       </c>
@@ -32608,7 +32624,7 @@
       <c r="C205" s="3" t="s">
         <v>486</v>
       </c>
-      <c r="D205" s="11">
+      <c r="D205" s="16">
         <v>243504046</v>
       </c>
       <c r="E205" s="3"/>
@@ -32628,7 +32644,7 @@
       <c r="S205" s="3"/>
     </row>
     <row r="206" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A206" s="9">
+      <c r="A206" s="11">
         <f t="shared" si="3"/>
         <v>203</v>
       </c>
@@ -32638,7 +32654,7 @@
       <c r="C206" s="3" t="s">
         <v>488</v>
       </c>
-      <c r="D206" s="11">
+      <c r="D206" s="16">
         <v>242971597</v>
       </c>
       <c r="E206" s="3"/>
@@ -32658,7 +32674,7 @@
       <c r="S206" s="3"/>
     </row>
     <row r="207" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A207" s="9">
+      <c r="A207" s="11">
         <f t="shared" si="3"/>
         <v>204</v>
       </c>
@@ -32668,7 +32684,7 @@
       <c r="C207" s="3" t="s">
         <v>490</v>
       </c>
-      <c r="D207" s="11">
+      <c r="D207" s="16">
         <v>242794262</v>
       </c>
       <c r="E207" s="3"/>
@@ -32688,7 +32704,7 @@
       <c r="S207" s="3"/>
     </row>
     <row r="208" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A208" s="9">
+      <c r="A208" s="11">
         <f t="shared" si="3"/>
         <v>205</v>
       </c>
@@ -32698,7 +32714,7 @@
       <c r="C208" s="3" t="s">
         <v>492</v>
       </c>
-      <c r="D208" s="11">
+      <c r="D208" s="16">
         <v>242517376</v>
       </c>
       <c r="E208" s="3"/>
@@ -32718,7 +32734,7 @@
       <c r="S208" s="3"/>
     </row>
     <row r="209" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A209" s="9">
+      <c r="A209" s="11">
         <f t="shared" si="3"/>
         <v>206</v>
       </c>
@@ -32728,7 +32744,7 @@
       <c r="C209" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="D209" s="11">
+      <c r="D209" s="16">
         <v>240572368</v>
       </c>
       <c r="E209" s="3"/>
@@ -32748,7 +32764,7 @@
       <c r="S209" s="3"/>
     </row>
     <row r="210" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A210" s="9">
+      <c r="A210" s="11">
         <f t="shared" si="3"/>
         <v>207</v>
       </c>
@@ -32758,7 +32774,7 @@
       <c r="C210" s="3" t="s">
         <v>496</v>
       </c>
-      <c r="D210" s="11">
+      <c r="D210" s="16">
         <v>237904880</v>
       </c>
       <c r="E210" s="3"/>
@@ -32778,7 +32794,7 @@
       <c r="S210" s="3"/>
     </row>
     <row r="211" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A211" s="9">
+      <c r="A211" s="11">
         <f t="shared" si="3"/>
         <v>208</v>
       </c>
@@ -32788,7 +32804,7 @@
       <c r="C211" s="3" t="s">
         <v>498</v>
       </c>
-      <c r="D211" s="11">
+      <c r="D211" s="16">
         <v>237335301</v>
       </c>
       <c r="E211" s="3"/>
@@ -32808,7 +32824,7 @@
       <c r="S211" s="3"/>
     </row>
     <row r="212" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A212" s="9">
+      <c r="A212" s="11">
         <f t="shared" si="3"/>
         <v>209</v>
       </c>
@@ -32818,7 +32834,7 @@
       <c r="C212" s="3" t="s">
         <v>500</v>
       </c>
-      <c r="D212" s="11">
+      <c r="D212" s="16">
         <v>232812165</v>
       </c>
       <c r="E212" s="3"/>
@@ -32838,7 +32854,7 @@
       <c r="S212" s="3"/>
     </row>
     <row r="213" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A213" s="9">
+      <c r="A213" s="11">
         <f t="shared" si="3"/>
         <v>210</v>
       </c>
@@ -32848,7 +32864,7 @@
       <c r="C213" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="D213" s="11">
+      <c r="D213" s="16">
         <v>232725616</v>
       </c>
       <c r="E213" s="3"/>
@@ -32868,7 +32884,7 @@
       <c r="S213" s="3"/>
     </row>
     <row r="214" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A214" s="9">
+      <c r="A214" s="11">
         <f t="shared" si="3"/>
         <v>211</v>
       </c>
@@ -32878,7 +32894,7 @@
       <c r="C214" s="3" t="s">
         <v>504</v>
       </c>
-      <c r="D214" s="11">
+      <c r="D214" s="16">
         <v>231534837</v>
       </c>
       <c r="E214" s="3"/>
@@ -32898,7 +32914,7 @@
       <c r="S214" s="3"/>
     </row>
     <row r="215" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A215" s="9">
+      <c r="A215" s="11">
         <f t="shared" si="3"/>
         <v>212</v>
       </c>
@@ -32908,7 +32924,7 @@
       <c r="C215" s="3" t="s">
         <v>506</v>
       </c>
-      <c r="D215" s="11">
+      <c r="D215" s="16">
         <v>228693120</v>
       </c>
       <c r="E215" s="3"/>
@@ -32928,7 +32944,7 @@
       <c r="S215" s="3"/>
     </row>
     <row r="216" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A216" s="9">
+      <c r="A216" s="11">
         <f t="shared" si="3"/>
         <v>213</v>
       </c>
@@ -32938,7 +32954,7 @@
       <c r="C216" s="3" t="s">
         <v>508</v>
       </c>
-      <c r="D216" s="11">
+      <c r="D216" s="16">
         <v>227761200</v>
       </c>
       <c r="E216" s="3"/>
@@ -32958,7 +32974,7 @@
       <c r="S216" s="3"/>
     </row>
     <row r="217" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A217" s="9">
+      <c r="A217" s="11">
         <f t="shared" si="3"/>
         <v>214</v>
       </c>
@@ -32968,7 +32984,7 @@
       <c r="C217" s="3" t="s">
         <v>510</v>
       </c>
-      <c r="D217" s="11">
+      <c r="D217" s="16">
         <v>227467958</v>
       </c>
       <c r="E217" s="3"/>
@@ -32988,7 +33004,7 @@
       <c r="S217" s="3"/>
     </row>
     <row r="218" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A218" s="9">
+      <c r="A218" s="11">
         <f t="shared" si="3"/>
         <v>215</v>
       </c>
@@ -32998,7 +33014,7 @@
       <c r="C218" s="3" t="s">
         <v>512</v>
       </c>
-      <c r="D218" s="11">
+      <c r="D218" s="16">
         <v>227159584</v>
       </c>
       <c r="E218" s="3"/>
@@ -33018,7 +33034,7 @@
       <c r="S218" s="3"/>
     </row>
     <row r="219" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A219" s="9">
+      <c r="A219" s="11">
         <f t="shared" si="3"/>
         <v>216</v>
       </c>
@@ -33028,7 +33044,7 @@
       <c r="C219" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="D219" s="11">
+      <c r="D219" s="16">
         <v>225610800</v>
       </c>
       <c r="E219" s="3"/>
@@ -33048,7 +33064,7 @@
       <c r="S219" s="3"/>
     </row>
     <row r="220" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A220" s="9">
+      <c r="A220" s="11">
         <f t="shared" si="3"/>
         <v>217</v>
       </c>
@@ -33058,7 +33074,7 @@
       <c r="C220" s="3" t="s">
         <v>516</v>
       </c>
-      <c r="D220" s="11">
+      <c r="D220" s="16">
         <v>225375808</v>
       </c>
       <c r="E220" s="3"/>
@@ -33078,7 +33094,7 @@
       <c r="S220" s="3"/>
     </row>
     <row r="221" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A221" s="9">
+      <c r="A221" s="11">
         <f t="shared" si="3"/>
         <v>218</v>
       </c>
@@ -33088,7 +33104,7 @@
       <c r="C221" s="3" t="s">
         <v>518</v>
       </c>
-      <c r="D221" s="11">
+      <c r="D221" s="16">
         <v>219778016</v>
       </c>
       <c r="E221" s="3"/>
@@ -33108,7 +33124,7 @@
       <c r="S221" s="3"/>
     </row>
     <row r="222" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A222" s="9">
+      <c r="A222" s="11">
         <f t="shared" si="3"/>
         <v>219</v>
       </c>
@@ -33118,7 +33134,7 @@
       <c r="C222" s="3" t="s">
         <v>520</v>
       </c>
-      <c r="D222" s="11">
+      <c r="D222" s="16">
         <v>216765136</v>
       </c>
       <c r="E222" s="3"/>
@@ -33138,7 +33154,7 @@
       <c r="S222" s="3"/>
     </row>
     <row r="223" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A223" s="9">
+      <c r="A223" s="11">
         <f t="shared" si="3"/>
         <v>220</v>
       </c>
@@ -33148,7 +33164,7 @@
       <c r="C223" s="3" t="s">
         <v>522</v>
       </c>
-      <c r="D223" s="11">
+      <c r="D223" s="16">
         <v>214474560</v>
       </c>
       <c r="E223" s="3"/>
@@ -33168,7 +33184,7 @@
       <c r="S223" s="3"/>
     </row>
     <row r="224" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A224" s="9">
+      <c r="A224" s="11">
         <f t="shared" si="3"/>
         <v>221</v>
       </c>
@@ -33178,7 +33194,7 @@
       <c r="C224" s="3" t="s">
         <v>524</v>
       </c>
-      <c r="D224" s="11">
+      <c r="D224" s="16">
         <v>211498966</v>
       </c>
       <c r="E224" s="3"/>
@@ -33198,7 +33214,7 @@
       <c r="S224" s="3"/>
     </row>
     <row r="225" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A225" s="9">
+      <c r="A225" s="11">
         <f t="shared" si="3"/>
         <v>222</v>
       </c>
@@ -33208,7 +33224,7 @@
       <c r="C225" s="3" t="s">
         <v>526</v>
       </c>
-      <c r="D225" s="11">
+      <c r="D225" s="16">
         <v>202001008</v>
       </c>
       <c r="E225" s="3"/>
@@ -33228,7 +33244,7 @@
       <c r="S225" s="3"/>
     </row>
     <row r="226" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A226" s="9">
+      <c r="A226" s="11">
         <f t="shared" si="3"/>
         <v>223</v>
       </c>
@@ -33238,7 +33254,7 @@
       <c r="C226" s="3" t="s">
         <v>528</v>
       </c>
-      <c r="D226" s="11">
+      <c r="D226" s="16">
         <v>194964591</v>
       </c>
       <c r="E226" s="3"/>
@@ -33258,7 +33274,7 @@
       <c r="S226" s="3"/>
     </row>
     <row r="227" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A227" s="9">
+      <c r="A227" s="11">
         <f t="shared" si="3"/>
         <v>224</v>
       </c>
@@ -33268,7 +33284,7 @@
       <c r="C227" s="3" t="s">
         <v>530</v>
       </c>
-      <c r="D227" s="11">
+      <c r="D227" s="16">
         <v>194849408</v>
       </c>
       <c r="E227" s="3"/>
@@ -33288,7 +33304,7 @@
       <c r="S227" s="3"/>
     </row>
     <row r="228" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A228" s="9">
+      <c r="A228" s="11">
         <f t="shared" si="3"/>
         <v>225</v>
       </c>
@@ -33298,7 +33314,7 @@
       <c r="C228" s="3" t="s">
         <v>532</v>
       </c>
-      <c r="D228" s="11">
+      <c r="D228" s="16">
         <v>192622040</v>
       </c>
       <c r="E228" s="3"/>
@@ -33318,7 +33334,7 @@
       <c r="S228" s="3"/>
     </row>
     <row r="229" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A229" s="9">
+      <c r="A229" s="11">
         <f t="shared" si="3"/>
         <v>226</v>
       </c>
@@ -33328,7 +33344,7 @@
       <c r="C229" s="3" t="s">
         <v>534</v>
       </c>
-      <c r="D229" s="11">
+      <c r="D229" s="16">
         <v>187924902</v>
       </c>
       <c r="E229" s="3"/>
@@ -33348,7 +33364,7 @@
       <c r="S229" s="3"/>
     </row>
     <row r="230" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A230" s="9">
+      <c r="A230" s="11">
         <f t="shared" si="3"/>
         <v>227</v>
       </c>
@@ -33358,7 +33374,7 @@
       <c r="C230" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="D230" s="11">
+      <c r="D230" s="16">
         <v>186182144</v>
       </c>
       <c r="E230" s="3"/>
@@ -33378,7 +33394,7 @@
       <c r="S230" s="3"/>
     </row>
     <row r="231" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A231" s="9">
+      <c r="A231" s="11">
         <f t="shared" si="3"/>
         <v>228</v>
       </c>
@@ -33388,7 +33404,7 @@
       <c r="C231" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="D231" s="11">
+      <c r="D231" s="16">
         <v>185994187</v>
       </c>
       <c r="E231" s="3"/>
@@ -33408,7 +33424,7 @@
       <c r="S231" s="3"/>
     </row>
     <row r="232" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A232" s="9">
+      <c r="A232" s="11">
         <f t="shared" si="3"/>
         <v>229</v>
       </c>
@@ -33418,7 +33434,7 @@
       <c r="C232" s="3" t="s">
         <v>540</v>
       </c>
-      <c r="D232" s="11">
+      <c r="D232" s="16">
         <v>183320454</v>
       </c>
       <c r="E232" s="3"/>
@@ -33438,7 +33454,7 @@
       <c r="S232" s="3"/>
     </row>
     <row r="233" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A233" s="9">
+      <c r="A233" s="11">
         <f t="shared" si="3"/>
         <v>230</v>
       </c>
@@ -33448,7 +33464,7 @@
       <c r="C233" s="3" t="s">
         <v>542</v>
       </c>
-      <c r="D233" s="11">
+      <c r="D233" s="16">
         <v>178256847</v>
       </c>
       <c r="E233" s="3"/>
@@ -33468,7 +33484,7 @@
       <c r="S233" s="3"/>
     </row>
     <row r="234" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A234" s="9">
+      <c r="A234" s="11">
         <f t="shared" si="3"/>
         <v>231</v>
       </c>
@@ -33478,7 +33494,7 @@
       <c r="C234" s="3" t="s">
         <v>544</v>
       </c>
-      <c r="D234" s="11">
+      <c r="D234" s="16">
         <v>167549614</v>
       </c>
       <c r="E234" s="3"/>
@@ -33498,7 +33514,7 @@
       <c r="S234" s="3"/>
     </row>
     <row r="235" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A235" s="9">
+      <c r="A235" s="11">
         <f t="shared" si="3"/>
         <v>232</v>
       </c>
@@ -33508,7 +33524,7 @@
       <c r="C235" s="3" t="s">
         <v>546</v>
       </c>
-      <c r="D235" s="11">
+      <c r="D235" s="16">
         <v>156949801</v>
       </c>
       <c r="E235" s="3"/>
@@ -33528,7 +33544,7 @@
       <c r="S235" s="3"/>
     </row>
     <row r="236" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A236" s="9">
+      <c r="A236" s="11">
         <f t="shared" si="3"/>
         <v>233</v>
       </c>
@@ -33538,7 +33554,7 @@
       <c r="C236" s="3" t="s">
         <v>548</v>
       </c>
-      <c r="D236" s="11">
+      <c r="D236" s="16">
         <v>151567616</v>
       </c>
       <c r="E236" s="3"/>
@@ -33558,7 +33574,7 @@
       <c r="S236" s="3"/>
     </row>
     <row r="237" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A237" s="9">
+      <c r="A237" s="11">
         <f t="shared" si="3"/>
         <v>234</v>
       </c>
@@ -33568,7 +33584,7 @@
       <c r="C237" s="3" t="s">
         <v>550</v>
       </c>
-      <c r="D237" s="11">
+      <c r="D237" s="16">
         <v>149217056</v>
       </c>
       <c r="E237" s="3"/>
@@ -33588,7 +33604,7 @@
       <c r="S237" s="3"/>
     </row>
     <row r="238" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A238" s="9">
+      <c r="A238" s="11">
         <f t="shared" si="3"/>
         <v>235</v>
       </c>
@@ -33598,7 +33614,7 @@
       <c r="C238" s="3" t="s">
         <v>552</v>
       </c>
-      <c r="D238" s="11">
+      <c r="D238" s="16">
         <v>144474278</v>
       </c>
       <c r="E238" s="3"/>
@@ -33618,7 +33634,7 @@
       <c r="S238" s="3"/>
     </row>
     <row r="239" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A239" s="9">
+      <c r="A239" s="11">
         <f t="shared" si="3"/>
         <v>236</v>
       </c>
@@ -33628,7 +33644,7 @@
       <c r="C239" s="3" t="s">
         <v>554</v>
       </c>
-      <c r="D239" s="11">
+      <c r="D239" s="16">
         <v>135180167</v>
       </c>
       <c r="E239" s="3"/>
@@ -33648,7 +33664,7 @@
       <c r="S239" s="3"/>
     </row>
     <row r="240" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A240" s="9">
+      <c r="A240" s="11">
         <f t="shared" si="3"/>
         <v>237</v>
       </c>
@@ -33658,7 +33674,7 @@
       <c r="C240" s="3" t="s">
         <v>556</v>
       </c>
-      <c r="D240" s="11">
+      <c r="D240" s="16">
         <v>133508648</v>
       </c>
       <c r="E240" s="3"/>
@@ -33678,7 +33694,7 @@
       <c r="S240" s="3"/>
     </row>
     <row r="241" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A241" s="9">
+      <c r="A241" s="11">
         <f t="shared" si="3"/>
         <v>238</v>
       </c>
@@ -33688,7 +33704,7 @@
       <c r="C241" s="3" t="s">
         <v>558</v>
       </c>
-      <c r="D241" s="11">
+      <c r="D241" s="16">
         <v>133433818</v>
       </c>
       <c r="E241" s="3"/>
@@ -33708,7 +33724,7 @@
       <c r="S241" s="3"/>
     </row>
     <row r="242" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A242" s="9">
+      <c r="A242" s="11">
         <f t="shared" si="3"/>
         <v>239</v>
       </c>
@@ -33718,7 +33734,7 @@
       <c r="C242" s="3" t="s">
         <v>560</v>
       </c>
-      <c r="D242" s="11">
+      <c r="D242" s="16">
         <v>132538736</v>
       </c>
       <c r="E242" s="3"/>
@@ -33738,7 +33754,7 @@
       <c r="S242" s="3"/>
     </row>
     <row r="243" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A243" s="9">
+      <c r="A243" s="11">
         <f t="shared" si="3"/>
         <v>240</v>
       </c>
@@ -33748,7 +33764,7 @@
       <c r="C243" s="3" t="s">
         <v>562</v>
       </c>
-      <c r="D243" s="11">
+      <c r="D243" s="16">
         <v>130689228</v>
       </c>
       <c r="E243" s="3"/>
@@ -33768,7 +33784,7 @@
       <c r="S243" s="3"/>
     </row>
     <row r="244" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A244" s="9">
+      <c r="A244" s="11">
         <f t="shared" si="3"/>
         <v>241</v>
       </c>
@@ -33778,7 +33794,7 @@
       <c r="C244" s="3" t="s">
         <v>564</v>
       </c>
-      <c r="D244" s="11">
+      <c r="D244" s="16">
         <v>129671592</v>
       </c>
       <c r="E244" s="3"/>
@@ -33798,7 +33814,7 @@
       <c r="S244" s="3"/>
     </row>
     <row r="245" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A245" s="9">
+      <c r="A245" s="11">
         <f t="shared" si="3"/>
         <v>242</v>
       </c>
@@ -33808,7 +33824,7 @@
       <c r="C245" s="3" t="s">
         <v>566</v>
       </c>
-      <c r="D245" s="11">
+      <c r="D245" s="16">
         <v>129645141</v>
       </c>
       <c r="E245" s="3"/>
@@ -33828,7 +33844,7 @@
       <c r="S245" s="3"/>
     </row>
     <row r="246" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A246" s="9">
+      <c r="A246" s="11">
         <f t="shared" si="3"/>
         <v>243</v>
       </c>
@@ -33838,7 +33854,7 @@
       <c r="C246" s="3" t="s">
         <v>568</v>
       </c>
-      <c r="D246" s="11">
+      <c r="D246" s="16">
         <v>128599095</v>
       </c>
       <c r="E246" s="3"/>
@@ -33858,7 +33874,7 @@
       <c r="S246" s="3"/>
     </row>
     <row r="247" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A247" s="9">
+      <c r="A247" s="11">
         <f t="shared" si="3"/>
         <v>244</v>
       </c>
@@ -33868,7 +33884,7 @@
       <c r="C247" s="3" t="s">
         <v>570</v>
       </c>
-      <c r="D247" s="11">
+      <c r="D247" s="16">
         <v>125110728</v>
       </c>
       <c r="E247" s="3"/>
@@ -33888,7 +33904,7 @@
       <c r="S247" s="3"/>
     </row>
     <row r="248" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A248" s="9">
+      <c r="A248" s="11">
         <f t="shared" si="3"/>
         <v>245</v>
       </c>
@@ -33898,7 +33914,7 @@
       <c r="C248" s="3" t="s">
         <v>572</v>
       </c>
-      <c r="D248" s="11">
+      <c r="D248" s="16">
         <v>124709690</v>
       </c>
       <c r="E248" s="3"/>
@@ -33918,7 +33934,7 @@
       <c r="S248" s="3"/>
     </row>
     <row r="249" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A249" s="9">
+      <c r="A249" s="11">
         <f t="shared" si="3"/>
         <v>246</v>
       </c>
@@ -33928,7 +33944,7 @@
       <c r="C249" s="3" t="s">
         <v>574</v>
       </c>
-      <c r="D249" s="11">
+      <c r="D249" s="16">
         <v>121381824</v>
       </c>
       <c r="E249" s="3"/>
@@ -33948,7 +33964,7 @@
       <c r="S249" s="3"/>
     </row>
     <row r="250" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A250" s="9">
+      <c r="A250" s="11">
         <f t="shared" si="3"/>
         <v>247</v>
       </c>
@@ -33958,7 +33974,7 @@
       <c r="C250" s="3" t="s">
         <v>576</v>
       </c>
-      <c r="D250" s="11">
+      <c r="D250" s="16">
         <v>120855152</v>
       </c>
       <c r="E250" s="3"/>
@@ -33978,7 +33994,7 @@
       <c r="S250" s="3"/>
     </row>
     <row r="251" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A251" s="9">
+      <c r="A251" s="11">
         <f t="shared" si="3"/>
         <v>248</v>
       </c>
@@ -33988,7 +34004,7 @@
       <c r="C251" s="3" t="s">
         <v>578</v>
       </c>
-      <c r="D251" s="11">
+      <c r="D251" s="16">
         <v>119170280</v>
       </c>
       <c r="E251" s="3"/>
@@ -34008,7 +34024,7 @@
       <c r="S251" s="3"/>
     </row>
     <row r="252" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A252" s="9">
+      <c r="A252" s="11">
         <f t="shared" si="3"/>
         <v>249</v>
       </c>
@@ -34018,7 +34034,7 @@
       <c r="C252" s="3" t="s">
         <v>580</v>
       </c>
-      <c r="D252" s="11">
+      <c r="D252" s="16">
         <v>116024520</v>
       </c>
       <c r="E252" s="3"/>
@@ -34038,7 +34054,7 @@
       <c r="S252" s="3"/>
     </row>
     <row r="253" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A253" s="9">
+      <c r="A253" s="11">
         <f t="shared" si="3"/>
         <v>250</v>
       </c>
@@ -34048,7 +34064,7 @@
       <c r="C253" s="3" t="s">
         <v>582</v>
       </c>
-      <c r="D253" s="11">
+      <c r="D253" s="16">
         <v>115077544</v>
       </c>
       <c r="E253" s="3"/>
@@ -34068,7 +34084,7 @@
       <c r="S253" s="3"/>
     </row>
     <row r="254" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A254" s="9">
+      <c r="A254" s="11">
         <f t="shared" si="3"/>
         <v>251</v>
       </c>
@@ -34078,7 +34094,7 @@
       <c r="C254" s="3" t="s">
         <v>584</v>
       </c>
-      <c r="D254" s="11">
+      <c r="D254" s="16">
         <v>113846292</v>
       </c>
       <c r="E254" s="3"/>
@@ -34098,7 +34114,7 @@
       <c r="S254" s="3"/>
     </row>
     <row r="255" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A255" s="9">
+      <c r="A255" s="11">
         <f t="shared" si="3"/>
         <v>252</v>
       </c>
@@ -34108,7 +34124,7 @@
       <c r="C255" s="3" t="s">
         <v>586</v>
       </c>
-      <c r="D255" s="11">
+      <c r="D255" s="16">
         <v>107701432</v>
       </c>
       <c r="E255" s="3"/>
@@ -34128,7 +34144,7 @@
       <c r="S255" s="3"/>
     </row>
     <row r="256" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A256" s="9">
+      <c r="A256" s="11">
         <f t="shared" si="3"/>
         <v>253</v>
       </c>
@@ -34138,7 +34154,7 @@
       <c r="C256" s="3" t="s">
         <v>588</v>
       </c>
-      <c r="D256" s="11">
+      <c r="D256" s="16">
         <v>107631130</v>
       </c>
       <c r="E256" s="3"/>
@@ -34158,7 +34174,7 @@
       <c r="S256" s="3"/>
     </row>
     <row r="257" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A257" s="9">
+      <c r="A257" s="11">
         <f t="shared" si="3"/>
         <v>254</v>
       </c>
@@ -34168,7 +34184,7 @@
       <c r="C257" s="3" t="s">
         <v>590</v>
       </c>
-      <c r="D257" s="11">
+      <c r="D257" s="16">
         <v>106719665</v>
       </c>
       <c r="E257" s="3"/>
@@ -34188,7 +34204,7 @@
       <c r="S257" s="3"/>
     </row>
     <row r="258" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A258" s="9">
+      <c r="A258" s="11">
         <f t="shared" si="3"/>
         <v>255</v>
       </c>
@@ -34198,7 +34214,7 @@
       <c r="C258" s="3" t="s">
         <v>592</v>
       </c>
-      <c r="D258" s="11">
+      <c r="D258" s="16">
         <v>104701384</v>
       </c>
       <c r="E258" s="3"/>
@@ -34218,7 +34234,7 @@
       <c r="S258" s="3"/>
     </row>
     <row r="259" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A259" s="9">
+      <c r="A259" s="11">
         <f t="shared" si="3"/>
         <v>256</v>
       </c>
@@ -34228,7 +34244,7 @@
       <c r="C259" s="3" t="s">
         <v>594</v>
       </c>
-      <c r="D259" s="11">
+      <c r="D259" s="16">
         <v>102586404</v>
       </c>
       <c r="E259" s="3"/>
@@ -34248,7 +34264,7 @@
       <c r="S259" s="3"/>
     </row>
     <row r="260" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A260" s="9">
+      <c r="A260" s="11">
         <f t="shared" si="3"/>
         <v>257</v>
       </c>
@@ -34258,7 +34274,7 @@
       <c r="C260" s="3" t="s">
         <v>596</v>
       </c>
-      <c r="D260" s="11">
+      <c r="D260" s="16">
         <v>98250251</v>
       </c>
       <c r="E260" s="3"/>
@@ -34278,7 +34294,7 @@
       <c r="S260" s="3"/>
     </row>
     <row r="261" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A261" s="9">
+      <c r="A261" s="11">
         <f t="shared" si="3"/>
         <v>258</v>
       </c>
@@ -34288,7 +34304,7 @@
       <c r="C261" s="3" t="s">
         <v>598</v>
       </c>
-      <c r="D261" s="11">
+      <c r="D261" s="16">
         <v>97206232</v>
       </c>
       <c r="E261" s="3"/>
@@ -34308,7 +34324,7 @@
       <c r="S261" s="3"/>
     </row>
     <row r="262" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A262" s="9">
+      <c r="A262" s="11">
         <f t="shared" ref="A262:A308" si="4">1+A261</f>
         <v>259</v>
       </c>
@@ -34318,7 +34334,7 @@
       <c r="C262" s="3" t="s">
         <v>600</v>
       </c>
-      <c r="D262" s="11">
+      <c r="D262" s="16">
         <v>90222136</v>
       </c>
       <c r="E262" s="3"/>
@@ -34338,7 +34354,7 @@
       <c r="S262" s="3"/>
     </row>
     <row r="263" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A263" s="9">
+      <c r="A263" s="11">
         <f t="shared" si="4"/>
         <v>260</v>
       </c>
@@ -34348,7 +34364,7 @@
       <c r="C263" s="3" t="s">
         <v>602</v>
       </c>
-      <c r="D263" s="11">
+      <c r="D263" s="16">
         <v>88754032</v>
       </c>
       <c r="E263" s="3"/>
@@ -34368,7 +34384,7 @@
       <c r="S263" s="3"/>
     </row>
     <row r="264" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A264" s="9">
+      <c r="A264" s="11">
         <f t="shared" si="4"/>
         <v>261</v>
       </c>
@@ -34378,7 +34394,7 @@
       <c r="C264" s="3" t="s">
         <v>604</v>
       </c>
-      <c r="D264" s="11">
+      <c r="D264" s="16">
         <v>81898152</v>
       </c>
       <c r="E264" s="3"/>
@@ -34398,7 +34414,7 @@
       <c r="S264" s="3"/>
     </row>
     <row r="265" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A265" s="9">
+      <c r="A265" s="11">
         <f t="shared" si="4"/>
         <v>262</v>
       </c>
@@ -34408,7 +34424,7 @@
       <c r="C265" s="3" t="s">
         <v>606</v>
       </c>
-      <c r="D265" s="11">
+      <c r="D265" s="16">
         <v>75823832</v>
       </c>
       <c r="E265" s="3"/>
@@ -34428,7 +34444,7 @@
       <c r="S265" s="3"/>
     </row>
     <row r="266" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A266" s="9">
+      <c r="A266" s="11">
         <f t="shared" si="4"/>
         <v>263</v>
       </c>
@@ -34438,7 +34454,7 @@
       <c r="C266" s="3" t="s">
         <v>608</v>
       </c>
-      <c r="D266" s="11">
+      <c r="D266" s="16">
         <v>71266013</v>
       </c>
       <c r="E266" s="3"/>
@@ -34458,7 +34474,7 @@
       <c r="S266" s="3"/>
     </row>
     <row r="267" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A267" s="9">
+      <c r="A267" s="11">
         <f t="shared" si="4"/>
         <v>264</v>
       </c>
@@ -34468,7 +34484,7 @@
       <c r="C267" s="3" t="s">
         <v>610</v>
       </c>
-      <c r="D267" s="11">
+      <c r="D267" s="16">
         <v>70703024</v>
       </c>
       <c r="E267" s="3"/>
@@ -34488,7 +34504,7 @@
       <c r="S267" s="3"/>
     </row>
     <row r="268" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A268" s="9">
+      <c r="A268" s="11">
         <f t="shared" si="4"/>
         <v>265</v>
       </c>
@@ -34498,7 +34514,7 @@
       <c r="C268" s="3" t="s">
         <v>612</v>
       </c>
-      <c r="D268" s="11">
+      <c r="D268" s="16">
         <v>70007728</v>
       </c>
       <c r="E268" s="3"/>
@@ -34518,7 +34534,7 @@
       <c r="S268" s="3"/>
     </row>
     <row r="269" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A269" s="9">
+      <c r="A269" s="11">
         <f t="shared" si="4"/>
         <v>266</v>
       </c>
@@ -34528,7 +34544,7 @@
       <c r="C269" s="3" t="s">
         <v>614</v>
       </c>
-      <c r="D269" s="11">
+      <c r="D269" s="16">
         <v>67382016</v>
       </c>
       <c r="E269" s="3"/>
@@ -34548,7 +34564,7 @@
       <c r="S269" s="3"/>
     </row>
     <row r="270" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A270" s="9">
+      <c r="A270" s="11">
         <f t="shared" si="4"/>
         <v>267</v>
       </c>
@@ -34558,7 +34574,7 @@
       <c r="C270" s="3" t="s">
         <v>616</v>
       </c>
-      <c r="D270" s="11">
+      <c r="D270" s="16">
         <v>66926006</v>
       </c>
       <c r="E270" s="3"/>
@@ -34578,7 +34594,7 @@
       <c r="S270" s="3"/>
     </row>
     <row r="271" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A271" s="9">
+      <c r="A271" s="11">
         <f t="shared" si="4"/>
         <v>268</v>
       </c>
@@ -34588,7 +34604,7 @@
       <c r="C271" s="3" t="s">
         <v>618</v>
       </c>
-      <c r="D271" s="11">
+      <c r="D271" s="16">
         <v>66158509</v>
       </c>
       <c r="E271" s="3"/>
@@ -34608,7 +34624,7 @@
       <c r="S271" s="3"/>
     </row>
     <row r="272" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A272" s="9">
+      <c r="A272" s="11">
         <f t="shared" si="4"/>
         <v>269</v>
       </c>
@@ -34618,7 +34634,7 @@
       <c r="C272" s="3" t="s">
         <v>620</v>
       </c>
-      <c r="D272" s="11">
+      <c r="D272" s="16">
         <v>65394221</v>
       </c>
       <c r="E272" s="3"/>
@@ -34638,7 +34654,7 @@
       <c r="S272" s="3"/>
     </row>
     <row r="273" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A273" s="9">
+      <c r="A273" s="11">
         <f t="shared" si="4"/>
         <v>270</v>
       </c>
@@ -34648,7 +34664,7 @@
       <c r="C273" s="3" t="s">
         <v>622</v>
       </c>
-      <c r="D273" s="11">
+      <c r="D273" s="16">
         <v>60616004</v>
       </c>
       <c r="E273" s="3"/>
@@ -34668,7 +34684,7 @@
       <c r="S273" s="3"/>
     </row>
     <row r="274" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A274" s="9">
+      <c r="A274" s="11">
         <f t="shared" si="4"/>
         <v>271</v>
       </c>
@@ -34678,7 +34694,7 @@
       <c r="C274" s="3" t="s">
         <v>624</v>
       </c>
-      <c r="D274" s="11">
+      <c r="D274" s="16">
         <v>57091332</v>
       </c>
       <c r="E274" s="3"/>
@@ -34698,7 +34714,7 @@
       <c r="S274" s="3"/>
     </row>
     <row r="275" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A275" s="9">
+      <c r="A275" s="11">
         <f t="shared" si="4"/>
         <v>272</v>
       </c>
@@ -34708,7 +34724,7 @@
       <c r="C275" s="3" t="s">
         <v>626</v>
       </c>
-      <c r="D275" s="11">
+      <c r="D275" s="16">
         <v>55504929</v>
       </c>
       <c r="E275" s="3"/>
@@ -34728,7 +34744,7 @@
       <c r="S275" s="3"/>
     </row>
     <row r="276" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A276" s="9">
+      <c r="A276" s="11">
         <f t="shared" si="4"/>
         <v>273</v>
       </c>
@@ -34738,7 +34754,7 @@
       <c r="C276" s="3" t="s">
         <v>628</v>
       </c>
-      <c r="D276" s="11">
+      <c r="D276" s="16">
         <v>54071794</v>
       </c>
       <c r="E276" s="3"/>
@@ -34758,7 +34774,7 @@
       <c r="S276" s="3"/>
     </row>
     <row r="277" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A277" s="9">
+      <c r="A277" s="11">
         <f t="shared" si="4"/>
         <v>274</v>
       </c>
@@ -34768,7 +34784,7 @@
       <c r="C277" s="3" t="s">
         <v>630</v>
       </c>
-      <c r="D277" s="11">
+      <c r="D277" s="16">
         <v>52325200</v>
       </c>
       <c r="E277" s="3"/>
@@ -34788,7 +34804,7 @@
       <c r="S277" s="3"/>
     </row>
     <row r="278" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A278" s="9">
+      <c r="A278" s="11">
         <f t="shared" si="4"/>
         <v>275</v>
       </c>
@@ -34798,7 +34814,7 @@
       <c r="C278" s="3" t="s">
         <v>632</v>
       </c>
-      <c r="D278" s="11">
+      <c r="D278" s="16">
         <v>50595568</v>
       </c>
       <c r="E278" s="3"/>
@@ -34818,7 +34834,7 @@
       <c r="S278" s="3"/>
     </row>
     <row r="279" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A279" s="9">
+      <c r="A279" s="11">
         <f t="shared" si="4"/>
         <v>276</v>
       </c>
@@ -34828,7 +34844,7 @@
       <c r="C279" s="3" t="s">
         <v>634</v>
       </c>
-      <c r="D279" s="11">
+      <c r="D279" s="16">
         <v>48620928</v>
       </c>
       <c r="E279" s="3"/>
@@ -34848,7 +34864,7 @@
       <c r="S279" s="3"/>
     </row>
     <row r="280" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A280" s="9">
+      <c r="A280" s="11">
         <f t="shared" si="4"/>
         <v>277</v>
       </c>
@@ -34858,7 +34874,7 @@
       <c r="C280" s="3" t="s">
         <v>636</v>
       </c>
-      <c r="D280" s="11">
+      <c r="D280" s="16">
         <v>46231824</v>
       </c>
       <c r="E280" s="3"/>
@@ -34878,7 +34894,7 @@
       <c r="S280" s="3"/>
     </row>
     <row r="281" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A281" s="9">
+      <c r="A281" s="11">
         <f t="shared" si="4"/>
         <v>278</v>
       </c>
@@ -34888,7 +34904,7 @@
       <c r="C281" s="3" t="s">
         <v>638</v>
       </c>
-      <c r="D281" s="11">
+      <c r="D281" s="16">
         <v>44511338</v>
       </c>
       <c r="E281" s="3"/>
@@ -34908,7 +34924,7 @@
       <c r="S281" s="3"/>
     </row>
     <row r="282" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A282" s="9">
+      <c r="A282" s="11">
         <f t="shared" si="4"/>
         <v>279</v>
       </c>
@@ -34918,7 +34934,7 @@
       <c r="C282" s="3" t="s">
         <v>640</v>
       </c>
-      <c r="D282" s="11">
+      <c r="D282" s="16">
         <v>37850618</v>
       </c>
       <c r="E282" s="3"/>
@@ -34938,7 +34954,7 @@
       <c r="S282" s="3"/>
     </row>
     <row r="283" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A283" s="9">
+      <c r="A283" s="11">
         <f t="shared" si="4"/>
         <v>280</v>
       </c>
@@ -34948,7 +34964,7 @@
       <c r="C283" s="3" t="s">
         <v>642</v>
       </c>
-      <c r="D283" s="11">
+      <c r="D283" s="16">
         <v>37843452</v>
       </c>
       <c r="E283" s="3"/>
@@ -34968,7 +34984,7 @@
       <c r="S283" s="3"/>
     </row>
     <row r="284" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A284" s="9">
+      <c r="A284" s="11">
         <f t="shared" si="4"/>
         <v>281</v>
       </c>
@@ -34978,7 +34994,7 @@
       <c r="C284" s="3" t="s">
         <v>644</v>
       </c>
-      <c r="D284" s="11">
+      <c r="D284" s="16">
         <v>21784470</v>
       </c>
       <c r="E284" s="3"/>
@@ -34998,7 +35014,7 @@
       <c r="S284" s="3"/>
     </row>
     <row r="285" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A285" s="9">
+      <c r="A285" s="11">
         <f t="shared" si="4"/>
         <v>282</v>
       </c>
@@ -35008,7 +35024,7 @@
       <c r="C285" s="3" t="s">
         <v>646</v>
       </c>
-      <c r="D285" s="11">
+      <c r="D285" s="16">
         <v>20102876</v>
       </c>
       <c r="E285" s="3"/>
@@ -35028,7 +35044,7 @@
       <c r="S285" s="3"/>
     </row>
     <row r="286" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A286" s="9">
+      <c r="A286" s="11">
         <f t="shared" si="4"/>
         <v>283</v>
       </c>
@@ -35038,7 +35054,7 @@
       <c r="C286" s="3" t="s">
         <v>648</v>
       </c>
-      <c r="D286" s="11">
+      <c r="D286" s="16">
         <v>17120622</v>
       </c>
       <c r="E286" s="3"/>
@@ -35058,7 +35074,7 @@
       <c r="S286" s="3"/>
     </row>
     <row r="287" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A287" s="9">
+      <c r="A287" s="11">
         <f t="shared" si="4"/>
         <v>284</v>
       </c>
@@ -35068,7 +35084,7 @@
       <c r="C287" s="3" t="s">
         <v>650</v>
       </c>
-      <c r="D287" s="11">
+      <c r="D287" s="16">
         <v>13246417</v>
       </c>
       <c r="E287" s="3"/>
@@ -35088,7 +35104,7 @@
       <c r="S287" s="3"/>
     </row>
     <row r="288" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A288" s="9">
+      <c r="A288" s="11">
         <f t="shared" si="4"/>
         <v>285</v>
       </c>
@@ -35098,7 +35114,7 @@
       <c r="C288" s="3" t="s">
         <v>652</v>
       </c>
-      <c r="D288" s="11">
+      <c r="D288" s="16">
         <v>12743325</v>
       </c>
       <c r="E288" s="3"/>
@@ -35118,7 +35134,7 @@
       <c r="S288" s="3"/>
     </row>
     <row r="289" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A289" s="9">
+      <c r="A289" s="11">
         <f t="shared" si="4"/>
         <v>286</v>
       </c>
@@ -35128,7 +35144,7 @@
       <c r="C289" s="3" t="s">
         <v>654</v>
       </c>
-      <c r="D289" s="11">
+      <c r="D289" s="16">
         <v>5910458</v>
       </c>
       <c r="E289" s="3"/>
@@ -35148,7 +35164,7 @@
       <c r="S289" s="3"/>
     </row>
     <row r="290" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A290" s="9">
+      <c r="A290" s="11">
         <f t="shared" si="4"/>
         <v>287</v>
       </c>
@@ -35158,7 +35174,7 @@
       <c r="C290" s="3" t="s">
         <v>656</v>
       </c>
-      <c r="D290" s="11">
+      <c r="D290" s="16">
         <v>5606911</v>
       </c>
       <c r="E290" s="3"/>
@@ -35178,7 +35194,7 @@
       <c r="S290" s="3"/>
     </row>
     <row r="291" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A291" s="9">
+      <c r="A291" s="11">
         <f t="shared" si="4"/>
         <v>288</v>
       </c>
@@ -35188,7 +35204,7 @@
       <c r="C291" s="3" t="s">
         <v>658</v>
       </c>
-      <c r="D291" s="11">
+      <c r="D291" s="16">
         <v>5021721</v>
       </c>
       <c r="E291" s="3"/>
@@ -35208,7 +35224,7 @@
       <c r="S291" s="3"/>
     </row>
     <row r="292" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A292" s="9">
+      <c r="A292" s="11">
         <f t="shared" si="4"/>
         <v>289</v>
       </c>
@@ -35218,7 +35234,7 @@
       <c r="C292" s="3" t="s">
         <v>660</v>
       </c>
-      <c r="D292" s="11">
+      <c r="D292" s="16">
         <v>3010600</v>
       </c>
       <c r="E292" s="3"/>
@@ -35238,7 +35254,7 @@
       <c r="S292" s="3"/>
     </row>
     <row r="293" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A293" s="9">
+      <c r="A293" s="11">
         <f t="shared" si="4"/>
         <v>290</v>
       </c>
@@ -35248,7 +35264,7 @@
       <c r="C293" s="3" t="s">
         <v>662</v>
       </c>
-      <c r="D293" s="11">
+      <c r="D293" s="16">
         <v>1714280</v>
       </c>
       <c r="E293" s="3"/>
@@ -35268,7 +35284,7 @@
       <c r="S293" s="3"/>
     </row>
     <row r="294" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A294" s="9">
+      <c r="A294" s="11">
         <f t="shared" si="4"/>
         <v>291</v>
       </c>
@@ -35278,7 +35294,7 @@
       <c r="C294" s="3" t="s">
         <v>664</v>
       </c>
-      <c r="D294" s="11">
+      <c r="D294" s="16">
         <v>775193</v>
       </c>
       <c r="E294" s="3"/>
@@ -35298,7 +35314,7 @@
       <c r="S294" s="3"/>
     </row>
     <row r="295" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A295" s="9">
+      <c r="A295" s="11">
         <f t="shared" si="4"/>
         <v>292</v>
       </c>
@@ -35328,7 +35344,7 @@
       <c r="S295" s="3"/>
     </row>
     <row r="296" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A296" s="9">
+      <c r="A296" s="11">
         <f t="shared" si="4"/>
         <v>293</v>
       </c>
@@ -35352,7 +35368,7 @@
       <c r="S296" s="3"/>
     </row>
     <row r="297" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A297" s="9">
+      <c r="A297" s="11">
         <f t="shared" si="4"/>
         <v>294</v>
       </c>
@@ -35376,7 +35392,7 @@
       <c r="S297" s="3"/>
     </row>
     <row r="298" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A298" s="9">
+      <c r="A298" s="11">
         <f t="shared" si="4"/>
         <v>295</v>
       </c>
@@ -35400,7 +35416,7 @@
       <c r="S298" s="3"/>
     </row>
     <row r="299" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A299" s="9">
+      <c r="A299" s="11">
         <f t="shared" si="4"/>
         <v>296</v>
       </c>
@@ -35424,7 +35440,7 @@
       <c r="S299" s="3"/>
     </row>
     <row r="300" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A300" s="9">
+      <c r="A300" s="11">
         <f t="shared" si="4"/>
         <v>297</v>
       </c>
@@ -35448,7 +35464,7 @@
       <c r="S300" s="3"/>
     </row>
     <row r="301" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A301" s="9">
+      <c r="A301" s="11">
         <f t="shared" si="4"/>
         <v>298</v>
       </c>
@@ -35472,7 +35488,7 @@
       <c r="S301" s="3"/>
     </row>
     <row r="302" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A302" s="9">
+      <c r="A302" s="11">
         <f t="shared" si="4"/>
         <v>299</v>
       </c>
@@ -35496,7 +35512,7 @@
       <c r="S302" s="3"/>
     </row>
     <row r="303" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A303" s="9">
+      <c r="A303" s="11">
         <f t="shared" si="4"/>
         <v>300</v>
       </c>
@@ -35520,7 +35536,7 @@
       <c r="S303" s="3"/>
     </row>
     <row r="304" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A304" s="9">
+      <c r="A304" s="11">
         <f t="shared" si="4"/>
         <v>301</v>
       </c>
@@ -35544,7 +35560,7 @@
       <c r="S304" s="3"/>
     </row>
     <row r="305" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A305" s="9">
+      <c r="A305" s="11">
         <f t="shared" si="4"/>
         <v>302</v>
       </c>
@@ -35568,7 +35584,7 @@
       <c r="S305" s="3"/>
     </row>
     <row r="306" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A306" s="9">
+      <c r="A306" s="11">
         <f t="shared" si="4"/>
         <v>303</v>
       </c>
@@ -35615,13 +35631,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF1BBA7C-6A7A-474E-826F-1875C86C1453}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="16384" width="9.140625" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="4" t="s">
         <v>64</v>
       </c>
     </row>

--- a/Materials.xlsx
+++ b/Materials.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8CE82AF-B7F6-453B-97B6-BE01B9232FE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AF3D6B7-06A5-4D85-9E41-98EFEE604CFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" activeTab="1" xr2:uid="{A6ACE955-0C4C-4110-BBCD-1B981A886B38}"/>
+    <workbookView xWindow="225" yWindow="1950" windowWidth="38175" windowHeight="15240" activeTab="1" xr2:uid="{A6ACE955-0C4C-4110-BBCD-1B981A886B38}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>

--- a/Materials.xlsx
+++ b/Materials.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AF3D6B7-06A5-4D85-9E41-98EFEE604CFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{780900CF-CA89-47C7-9605-63DD1FBBA959}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="1950" windowWidth="38175" windowHeight="15240" activeTab="1" xr2:uid="{A6ACE955-0C4C-4110-BBCD-1B981A886B38}"/>
+    <workbookView xWindow="225" yWindow="2730" windowWidth="38175" windowHeight="15240" activeTab="1" xr2:uid="{A6ACE955-0C4C-4110-BBCD-1B981A886B38}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -2225,6 +2225,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -2264,6 +2265,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -2303,6 +2305,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>

--- a/Materials.xlsx
+++ b/Materials.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{780900CF-CA89-47C7-9605-63DD1FBBA959}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{131A93A1-7A3A-49B4-8491-C18A9942D9C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="2730" windowWidth="38175" windowHeight="15240" activeTab="1" xr2:uid="{A6ACE955-0C4C-4110-BBCD-1B981A886B38}"/>
+    <workbookView xWindow="225" yWindow="2730" windowWidth="38175" windowHeight="15240" activeTab="2" xr2:uid="{A6ACE955-0C4C-4110-BBCD-1B981A886B38}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -343,9 +343,6 @@
     <t>Switzerland</t>
   </si>
   <si>
-    <t>Grupo MÃ©xico</t>
-  </si>
-  <si>
     <t>GMBXF</t>
   </si>
   <si>
@@ -2048,6 +2045,9 @@
   </si>
   <si>
     <t>Q125</t>
+  </si>
+  <si>
+    <t>Grupo Mexico</t>
   </si>
 </sst>
 </file>
@@ -2058,13 +2058,19 @@
     <numFmt numFmtId="164" formatCode="#,##0.0;\(#,##0.0\)"/>
     <numFmt numFmtId="165" formatCode="#,##0;\(#,##0\)"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -2170,38 +2176,39 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -3554,7 +3561,7 @@
         <v>40889.167902739995</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
@@ -26741,7 +26748,7 @@
         <v>84203.101320499991</v>
       </c>
       <c r="I7" s="15" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
@@ -26999,14 +27006,14 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="17" t="s">
+        <v>667</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>101</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -27030,10 +27037,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>102</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>103</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>84</v>
@@ -27060,10 +27067,10 @@
         <v>15</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>104</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>105</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>84</v>
@@ -27090,10 +27097,10 @@
         <v>16</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>106</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>107</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>74</v>
@@ -27120,10 +27127,10 @@
         <v>17</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>108</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>109</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>84</v>
@@ -27150,10 +27157,10 @@
         <v>18</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>111</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>68</v>
@@ -27180,13 +27187,13 @@
         <v>19</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="D22" s="3" t="s">
         <v>113</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>114</v>
       </c>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
@@ -27210,10 +27217,10 @@
         <v>20</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>116</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>84</v>
@@ -27240,13 +27247,13 @@
         <v>21</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="D24" s="3" t="s">
         <v>118</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>119</v>
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
@@ -27270,13 +27277,13 @@
         <v>22</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="D25" s="3" t="s">
         <v>121</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>122</v>
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
@@ -27300,13 +27307,13 @@
         <v>23</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>124</v>
-      </c>
       <c r="D26" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
@@ -27330,10 +27337,10 @@
         <v>24</v>
       </c>
       <c r="B27" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>126</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>74</v>
@@ -27360,13 +27367,13 @@
         <v>25</v>
       </c>
       <c r="B28" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="C28" s="3" t="s">
-        <v>128</v>
-      </c>
       <c r="D28" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
@@ -27390,10 +27397,10 @@
         <v>26</v>
       </c>
       <c r="B29" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>129</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>130</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>71</v>
@@ -27420,10 +27427,10 @@
         <v>27</v>
       </c>
       <c r="B30" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>131</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>132</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>84</v>
@@ -27450,10 +27457,10 @@
         <v>28</v>
       </c>
       <c r="B31" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>133</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>134</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>84</v>
@@ -27480,10 +27487,10 @@
         <v>29</v>
       </c>
       <c r="B32" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C32" s="3" t="s">
         <v>135</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>136</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>84</v>
@@ -27510,10 +27517,10 @@
         <v>30</v>
       </c>
       <c r="B33" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>137</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>138</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>68</v>
@@ -27540,10 +27547,10 @@
         <v>31</v>
       </c>
       <c r="B34" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>139</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>140</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>71</v>
@@ -27570,10 +27577,10 @@
         <v>32</v>
       </c>
       <c r="B35" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>141</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>142</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>84</v>
@@ -27600,10 +27607,10 @@
         <v>33</v>
       </c>
       <c r="B36" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>143</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>144</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>77</v>
@@ -27630,10 +27637,10 @@
         <v>34</v>
       </c>
       <c r="B37" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>84</v>
@@ -27660,13 +27667,13 @@
         <v>35</v>
       </c>
       <c r="B38" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="C38" s="3" t="s">
-        <v>148</v>
-      </c>
       <c r="D38" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
@@ -27690,13 +27697,13 @@
         <v>36</v>
       </c>
       <c r="B39" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C39" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="C39" s="3" t="s">
-        <v>150</v>
-      </c>
       <c r="D39" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
@@ -27720,10 +27727,10 @@
         <v>37</v>
       </c>
       <c r="B40" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>151</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>152</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>68</v>
@@ -27750,10 +27757,10 @@
         <v>38</v>
       </c>
       <c r="B41" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>153</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>154</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>84</v>
@@ -27780,13 +27787,13 @@
         <v>39</v>
       </c>
       <c r="B42" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C42" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="D42" s="3" t="s">
         <v>156</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>157</v>
       </c>
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
@@ -27810,10 +27817,10 @@
         <v>40</v>
       </c>
       <c r="B43" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C43" s="3" t="s">
         <v>158</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>159</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>84</v>
@@ -27840,13 +27847,13 @@
         <v>41</v>
       </c>
       <c r="B44" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C44" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="C44" s="3" t="s">
-        <v>161</v>
-      </c>
       <c r="D44" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
@@ -27870,10 +27877,10 @@
         <v>42</v>
       </c>
       <c r="B45" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C45" s="3" t="s">
         <v>162</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>163</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>84</v>
@@ -27900,10 +27907,10 @@
         <v>43</v>
       </c>
       <c r="B46" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>164</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>165</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>68</v>
@@ -27930,13 +27937,13 @@
         <v>44</v>
       </c>
       <c r="B47" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C47" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="D47" s="3" t="s">
         <v>167</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>168</v>
       </c>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
@@ -27960,10 +27967,10 @@
         <v>45</v>
       </c>
       <c r="B48" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C48" s="3" t="s">
         <v>169</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>170</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>71</v>
@@ -27990,10 +27997,10 @@
         <v>46</v>
       </c>
       <c r="B49" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C49" s="3" t="s">
         <v>171</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>172</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>68</v>
@@ -28020,13 +28027,13 @@
         <v>47</v>
       </c>
       <c r="B50" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="C50" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="D50" s="3" t="s">
         <v>174</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>175</v>
       </c>
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
@@ -28050,13 +28057,13 @@
         <v>48</v>
       </c>
       <c r="B51" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C51" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="C51" s="3" t="s">
-        <v>177</v>
-      </c>
       <c r="D51" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
@@ -28080,10 +28087,10 @@
         <v>49</v>
       </c>
       <c r="B52" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C52" s="3" t="s">
         <v>178</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>179</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>74</v>
@@ -28110,10 +28117,10 @@
         <v>50</v>
       </c>
       <c r="B53" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C53" s="3" t="s">
         <v>180</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>181</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>84</v>
@@ -28140,13 +28147,13 @@
         <v>51</v>
       </c>
       <c r="B54" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C54" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="C54" s="3" t="s">
-        <v>183</v>
-      </c>
       <c r="D54" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
@@ -28170,13 +28177,13 @@
         <v>52</v>
       </c>
       <c r="B55" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C55" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="D55" s="3" t="s">
         <v>185</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>186</v>
       </c>
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
@@ -28200,10 +28207,10 @@
         <v>53</v>
       </c>
       <c r="B56" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C56" s="3" t="s">
         <v>187</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>188</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>71</v>
@@ -28230,10 +28237,10 @@
         <v>54</v>
       </c>
       <c r="B57" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C57" s="3" t="s">
         <v>189</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>190</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>95</v>
@@ -28260,13 +28267,13 @@
         <v>55</v>
       </c>
       <c r="B58" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C58" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="C58" s="3" t="s">
+      <c r="D58" s="3" t="s">
         <v>192</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>193</v>
       </c>
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
@@ -28290,10 +28297,10 @@
         <v>56</v>
       </c>
       <c r="B59" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C59" s="3" t="s">
         <v>194</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>195</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>92</v>
@@ -28320,10 +28327,10 @@
         <v>57</v>
       </c>
       <c r="B60" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C60" s="3" t="s">
         <v>196</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>197</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>68</v>
@@ -28350,10 +28357,10 @@
         <v>58</v>
       </c>
       <c r="B61" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C61" s="3" t="s">
         <v>198</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>199</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>84</v>
@@ -28380,10 +28387,10 @@
         <v>59</v>
       </c>
       <c r="B62" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="C62" s="3" t="s">
         <v>200</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>201</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>84</v>
@@ -28410,10 +28417,10 @@
         <v>60</v>
       </c>
       <c r="B63" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C63" s="3" t="s">
         <v>202</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>203</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>84</v>
@@ -28440,10 +28447,10 @@
         <v>61</v>
       </c>
       <c r="B64" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="C64" s="3" t="s">
         <v>204</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>205</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>68</v>
@@ -28470,10 +28477,10 @@
         <v>62</v>
       </c>
       <c r="B65" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C65" s="3" t="s">
         <v>206</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>207</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>84</v>
@@ -28500,10 +28507,10 @@
         <v>63</v>
       </c>
       <c r="B66" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="C66" s="3" t="s">
         <v>208</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>209</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>77</v>
@@ -28530,10 +28537,10 @@
         <v>64</v>
       </c>
       <c r="B67" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C67" s="3" t="s">
         <v>210</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>211</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>68</v>
@@ -28560,13 +28567,13 @@
         <v>65</v>
       </c>
       <c r="B68" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C68" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="C68" s="3" t="s">
-        <v>213</v>
-      </c>
       <c r="D68" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
@@ -28590,10 +28597,10 @@
         <v>66</v>
       </c>
       <c r="B69" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C69" s="3" t="s">
         <v>214</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>215</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>77</v>
@@ -28620,13 +28627,13 @@
         <v>67</v>
       </c>
       <c r="B70" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="C70" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="C70" s="3" t="s">
+      <c r="D70" s="3" t="s">
         <v>217</v>
-      </c>
-      <c r="D70" s="3" t="s">
-        <v>218</v>
       </c>
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
@@ -28650,10 +28657,10 @@
         <v>68</v>
       </c>
       <c r="B71" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="C71" s="3" t="s">
         <v>219</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>220</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>77</v>
@@ -28680,10 +28687,10 @@
         <v>69</v>
       </c>
       <c r="B72" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="C72" s="3" t="s">
         <v>221</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>222</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>77</v>
@@ -28710,10 +28717,10 @@
         <v>70</v>
       </c>
       <c r="B73" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C73" s="3" t="s">
         <v>223</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>224</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>77</v>
@@ -28740,10 +28747,10 @@
         <v>71</v>
       </c>
       <c r="B74" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="C74" s="3" t="s">
         <v>225</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>226</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>84</v>
@@ -28770,10 +28777,10 @@
         <v>72</v>
       </c>
       <c r="B75" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="C75" s="3" t="s">
         <v>227</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>228</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>84</v>
@@ -28800,10 +28807,10 @@
         <v>73</v>
       </c>
       <c r="B76" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="C76" s="3" t="s">
         <v>229</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>230</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>84</v>
@@ -28830,10 +28837,10 @@
         <v>74</v>
       </c>
       <c r="B77" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="C77" s="3" t="s">
         <v>231</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>232</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>84</v>
@@ -28860,10 +28867,10 @@
         <v>75</v>
       </c>
       <c r="B78" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C78" s="3" t="s">
         <v>233</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>234</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>68</v>
@@ -28890,10 +28897,10 @@
         <v>76</v>
       </c>
       <c r="B79" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="C79" s="3" t="s">
         <v>235</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>236</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>68</v>
@@ -28920,13 +28927,13 @@
         <v>77</v>
       </c>
       <c r="B80" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="C80" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="C80" s="3" t="s">
-        <v>238</v>
-      </c>
       <c r="D80" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E80" s="3"/>
       <c r="F80" s="3"/>
@@ -28950,10 +28957,10 @@
         <v>78</v>
       </c>
       <c r="B81" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C81" s="3" t="s">
         <v>239</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>240</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>84</v>
@@ -28980,10 +28987,10 @@
         <v>79</v>
       </c>
       <c r="B82" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="C82" s="3" t="s">
         <v>241</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>242</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>68</v>
@@ -29010,10 +29017,10 @@
         <v>80</v>
       </c>
       <c r="B83" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="C83" s="3" t="s">
         <v>243</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>244</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>84</v>
@@ -29040,10 +29047,10 @@
         <v>81</v>
       </c>
       <c r="B84" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="C84" s="3" t="s">
         <v>245</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>246</v>
       </c>
       <c r="D84" s="3" t="s">
         <v>84</v>
@@ -29070,10 +29077,10 @@
         <v>82</v>
       </c>
       <c r="B85" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="C85" s="3" t="s">
         <v>247</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>248</v>
       </c>
       <c r="D85" s="3" t="s">
         <v>68</v>
@@ -29100,10 +29107,10 @@
         <v>83</v>
       </c>
       <c r="B86" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C86" s="3" t="s">
         <v>249</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>250</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>84</v>
@@ -29130,10 +29137,10 @@
         <v>84</v>
       </c>
       <c r="B87" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="C87" s="3" t="s">
         <v>251</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>252</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>84</v>
@@ -29160,13 +29167,13 @@
         <v>85</v>
       </c>
       <c r="B88" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="C88" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="C88" s="3" t="s">
+      <c r="D88" s="3" t="s">
         <v>254</v>
-      </c>
-      <c r="D88" s="3" t="s">
-        <v>255</v>
       </c>
       <c r="E88" s="3"/>
       <c r="F88" s="3"/>
@@ -29190,10 +29197,10 @@
         <v>86</v>
       </c>
       <c r="B89" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="C89" s="3" t="s">
         <v>256</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>257</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>74</v>
@@ -29220,10 +29227,10 @@
         <v>87</v>
       </c>
       <c r="B90" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C90" s="3" t="s">
         <v>258</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>259</v>
       </c>
       <c r="D90" s="3" t="s">
         <v>84</v>
@@ -29250,10 +29257,10 @@
         <v>88</v>
       </c>
       <c r="B91" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="C91" s="3" t="s">
         <v>260</v>
-      </c>
-      <c r="C91" s="3" t="s">
-        <v>261</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>77</v>
@@ -29280,10 +29287,10 @@
         <v>89</v>
       </c>
       <c r="B92" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C92" s="3" t="s">
         <v>262</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>263</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>84</v>
@@ -29310,13 +29317,13 @@
         <v>90</v>
       </c>
       <c r="B93" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C93" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="C93" s="3" t="s">
-        <v>265</v>
-      </c>
       <c r="D93" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E93" s="3"/>
       <c r="F93" s="3"/>
@@ -29340,10 +29347,10 @@
         <v>91</v>
       </c>
       <c r="B94" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="C94" s="3" t="s">
         <v>266</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>267</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>84</v>
@@ -29370,10 +29377,10 @@
         <v>92</v>
       </c>
       <c r="B95" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="C95" s="3" t="s">
         <v>268</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>269</v>
       </c>
       <c r="D95" s="3" t="s">
         <v>68</v>
@@ -29400,10 +29407,10 @@
         <v>93</v>
       </c>
       <c r="B96" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C96" s="3" t="s">
         <v>270</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>271</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>84</v>
@@ -29430,10 +29437,10 @@
         <v>94</v>
       </c>
       <c r="B97" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="C97" s="3" t="s">
         <v>272</v>
-      </c>
-      <c r="C97" s="3" t="s">
-        <v>273</v>
       </c>
       <c r="D97" s="3" t="s">
         <v>68</v>
@@ -29460,10 +29467,10 @@
         <v>95</v>
       </c>
       <c r="B98" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="C98" s="3" t="s">
         <v>274</v>
-      </c>
-      <c r="C98" s="3" t="s">
-        <v>275</v>
       </c>
       <c r="D98" s="3" t="s">
         <v>68</v>
@@ -29490,13 +29497,13 @@
         <v>96</v>
       </c>
       <c r="B99" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="C99" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="C99" s="3" t="s">
-        <v>277</v>
-      </c>
       <c r="D99" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E99" s="3"/>
       <c r="F99" s="3"/>
@@ -29520,10 +29527,10 @@
         <v>97</v>
       </c>
       <c r="B100" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="C100" s="3" t="s">
         <v>278</v>
-      </c>
-      <c r="C100" s="3" t="s">
-        <v>279</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>74</v>
@@ -29550,10 +29557,10 @@
         <v>98</v>
       </c>
       <c r="B101" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="C101" s="3" t="s">
         <v>280</v>
-      </c>
-      <c r="C101" s="3" t="s">
-        <v>281</v>
       </c>
       <c r="D101" s="3" t="s">
         <v>68</v>
@@ -29580,10 +29587,10 @@
         <v>99</v>
       </c>
       <c r="B102" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="C102" s="3" t="s">
         <v>282</v>
-      </c>
-      <c r="C102" s="3" t="s">
-        <v>283</v>
       </c>
       <c r="D102" s="3" t="s">
         <v>68</v>
@@ -29610,10 +29617,10 @@
         <v>100</v>
       </c>
       <c r="B103" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="C103" s="3" t="s">
         <v>284</v>
-      </c>
-      <c r="C103" s="3" t="s">
-        <v>285</v>
       </c>
       <c r="D103" s="3" t="s">
         <v>84</v>
@@ -29640,10 +29647,10 @@
         <v>101</v>
       </c>
       <c r="B104" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="C104" s="3" t="s">
         <v>286</v>
-      </c>
-      <c r="C104" s="3" t="s">
-        <v>287</v>
       </c>
       <c r="D104" s="3" t="s">
         <v>68</v>
@@ -29670,10 +29677,10 @@
         <v>102</v>
       </c>
       <c r="B105" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C105" s="3" t="s">
         <v>288</v>
-      </c>
-      <c r="C105" s="3" t="s">
-        <v>289</v>
       </c>
       <c r="D105" s="3" t="s">
         <v>92</v>
@@ -29700,10 +29707,10 @@
         <v>103</v>
       </c>
       <c r="B106" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="C106" s="3" t="s">
         <v>290</v>
-      </c>
-      <c r="C106" s="3" t="s">
-        <v>291</v>
       </c>
       <c r="D106" s="3" t="s">
         <v>77</v>
@@ -29730,10 +29737,10 @@
         <v>104</v>
       </c>
       <c r="B107" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="C107" s="3" t="s">
         <v>292</v>
-      </c>
-      <c r="C107" s="3" t="s">
-        <v>293</v>
       </c>
       <c r="D107" s="3" t="s">
         <v>84</v>
@@ -29760,13 +29767,13 @@
         <v>105</v>
       </c>
       <c r="B108" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="C108" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="C108" s="3" t="s">
-        <v>295</v>
-      </c>
       <c r="D108" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E108" s="3"/>
       <c r="F108" s="3"/>
@@ -29790,10 +29797,10 @@
         <v>106</v>
       </c>
       <c r="B109" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="C109" s="3" t="s">
         <v>296</v>
-      </c>
-      <c r="C109" s="3" t="s">
-        <v>297</v>
       </c>
       <c r="D109" s="3" t="s">
         <v>84</v>
@@ -29820,10 +29827,10 @@
         <v>107</v>
       </c>
       <c r="B110" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="C110" s="3" t="s">
         <v>298</v>
-      </c>
-      <c r="C110" s="3" t="s">
-        <v>299</v>
       </c>
       <c r="D110" s="3" t="s">
         <v>68</v>
@@ -29850,10 +29857,10 @@
         <v>108</v>
       </c>
       <c r="B111" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="C111" s="3" t="s">
         <v>300</v>
-      </c>
-      <c r="C111" s="3" t="s">
-        <v>301</v>
       </c>
       <c r="D111" s="3" t="s">
         <v>84</v>
@@ -29880,10 +29887,10 @@
         <v>109</v>
       </c>
       <c r="B112" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="C112" s="3" t="s">
         <v>302</v>
-      </c>
-      <c r="C112" s="3" t="s">
-        <v>303</v>
       </c>
       <c r="D112" s="3" t="s">
         <v>68</v>
@@ -29910,10 +29917,10 @@
         <v>110</v>
       </c>
       <c r="B113" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="C113" s="3" t="s">
         <v>304</v>
-      </c>
-      <c r="C113" s="3" t="s">
-        <v>305</v>
       </c>
       <c r="D113" s="3" t="s">
         <v>68</v>
@@ -29940,13 +29947,13 @@
         <v>111</v>
       </c>
       <c r="B114" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="C114" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="C114" s="3" t="s">
-        <v>307</v>
-      </c>
       <c r="D114" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E114" s="3"/>
       <c r="F114" s="3"/>
@@ -29970,13 +29977,13 @@
         <v>112</v>
       </c>
       <c r="B115" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="C115" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="C115" s="3" t="s">
-        <v>309</v>
-      </c>
       <c r="D115" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E115" s="3"/>
       <c r="F115" s="3"/>
@@ -30000,10 +30007,10 @@
         <v>113</v>
       </c>
       <c r="B116" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="C116" s="3" t="s">
         <v>310</v>
-      </c>
-      <c r="C116" s="3" t="s">
-        <v>311</v>
       </c>
       <c r="D116" s="3" t="s">
         <v>84</v>
@@ -30030,7 +30037,7 @@
         <v>114</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C117" s="3"/>
       <c r="D117" s="3"/>
@@ -30056,10 +30063,10 @@
         <v>115</v>
       </c>
       <c r="B118" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="C118" s="3" t="s">
         <v>313</v>
-      </c>
-      <c r="C118" s="3" t="s">
-        <v>314</v>
       </c>
       <c r="D118" s="16"/>
       <c r="E118" s="3"/>
@@ -30084,10 +30091,10 @@
         <v>116</v>
       </c>
       <c r="B119" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="C119" s="3" t="s">
         <v>315</v>
-      </c>
-      <c r="C119" s="3" t="s">
-        <v>316</v>
       </c>
       <c r="D119" s="16"/>
       <c r="E119" s="3"/>
@@ -30112,10 +30119,10 @@
         <v>117</v>
       </c>
       <c r="B120" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="C120" s="3" t="s">
         <v>317</v>
-      </c>
-      <c r="C120" s="3" t="s">
-        <v>318</v>
       </c>
       <c r="D120" s="16"/>
       <c r="E120" s="3"/>
@@ -30140,10 +30147,10 @@
         <v>118</v>
       </c>
       <c r="B121" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="C121" s="3" t="s">
         <v>319</v>
-      </c>
-      <c r="C121" s="3" t="s">
-        <v>320</v>
       </c>
       <c r="D121" s="16"/>
       <c r="E121" s="3"/>
@@ -30168,10 +30175,10 @@
         <v>119</v>
       </c>
       <c r="B122" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="C122" s="3" t="s">
         <v>321</v>
-      </c>
-      <c r="C122" s="3" t="s">
-        <v>322</v>
       </c>
       <c r="D122" s="16"/>
       <c r="E122" s="3"/>
@@ -30196,10 +30203,10 @@
         <v>120</v>
       </c>
       <c r="B123" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="C123" s="3" t="s">
         <v>323</v>
-      </c>
-      <c r="C123" s="3" t="s">
-        <v>324</v>
       </c>
       <c r="D123" s="16"/>
       <c r="E123" s="3"/>
@@ -30224,10 +30231,10 @@
         <v>121</v>
       </c>
       <c r="B124" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C124" s="3" t="s">
         <v>325</v>
-      </c>
-      <c r="C124" s="3" t="s">
-        <v>326</v>
       </c>
       <c r="D124" s="16"/>
       <c r="E124" s="3"/>
@@ -30252,10 +30259,10 @@
         <v>122</v>
       </c>
       <c r="B125" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="C125" s="3" t="s">
         <v>327</v>
-      </c>
-      <c r="C125" s="3" t="s">
-        <v>328</v>
       </c>
       <c r="D125" s="16"/>
       <c r="E125" s="3"/>
@@ -30280,10 +30287,10 @@
         <v>123</v>
       </c>
       <c r="B126" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="C126" s="3" t="s">
         <v>329</v>
-      </c>
-      <c r="C126" s="3" t="s">
-        <v>330</v>
       </c>
       <c r="D126" s="16"/>
       <c r="E126" s="3"/>
@@ -30308,10 +30315,10 @@
         <v>124</v>
       </c>
       <c r="B127" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="C127" s="3" t="s">
         <v>331</v>
-      </c>
-      <c r="C127" s="3" t="s">
-        <v>332</v>
       </c>
       <c r="D127" s="16"/>
       <c r="E127" s="3"/>
@@ -30336,10 +30343,10 @@
         <v>125</v>
       </c>
       <c r="B128" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="C128" s="3" t="s">
         <v>333</v>
-      </c>
-      <c r="C128" s="3" t="s">
-        <v>334</v>
       </c>
       <c r="D128" s="16"/>
       <c r="E128" s="3"/>
@@ -30364,10 +30371,10 @@
         <v>126</v>
       </c>
       <c r="B129" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="C129" s="3" t="s">
         <v>335</v>
-      </c>
-      <c r="C129" s="3" t="s">
-        <v>336</v>
       </c>
       <c r="D129" s="16"/>
       <c r="E129" s="3"/>
@@ -30392,10 +30399,10 @@
         <v>127</v>
       </c>
       <c r="B130" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="C130" s="3" t="s">
         <v>337</v>
-      </c>
-      <c r="C130" s="3" t="s">
-        <v>338</v>
       </c>
       <c r="D130" s="16"/>
       <c r="E130" s="3"/>
@@ -30420,10 +30427,10 @@
         <v>128</v>
       </c>
       <c r="B131" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="C131" s="3" t="s">
         <v>339</v>
-      </c>
-      <c r="C131" s="3" t="s">
-        <v>340</v>
       </c>
       <c r="D131" s="16"/>
       <c r="E131" s="3"/>
@@ -30448,10 +30455,10 @@
         <v>129</v>
       </c>
       <c r="B132" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="C132" s="3" t="s">
         <v>341</v>
-      </c>
-      <c r="C132" s="3" t="s">
-        <v>342</v>
       </c>
       <c r="D132" s="16"/>
       <c r="E132" s="3"/>
@@ -30476,10 +30483,10 @@
         <v>130</v>
       </c>
       <c r="B133" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="C133" s="3" t="s">
         <v>343</v>
-      </c>
-      <c r="C133" s="3" t="s">
-        <v>344</v>
       </c>
       <c r="D133" s="16"/>
       <c r="E133" s="3"/>
@@ -30504,10 +30511,10 @@
         <v>131</v>
       </c>
       <c r="B134" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="C134" s="3" t="s">
         <v>345</v>
-      </c>
-      <c r="C134" s="3" t="s">
-        <v>346</v>
       </c>
       <c r="D134" s="16"/>
       <c r="E134" s="3"/>
@@ -30532,10 +30539,10 @@
         <v>132</v>
       </c>
       <c r="B135" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="C135" s="3" t="s">
         <v>347</v>
-      </c>
-      <c r="C135" s="3" t="s">
-        <v>348</v>
       </c>
       <c r="D135" s="16"/>
       <c r="E135" s="3"/>
@@ -30560,7 +30567,7 @@
         <v>133</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C136" s="3"/>
       <c r="D136" s="3"/>
@@ -30586,10 +30593,10 @@
         <v>134</v>
       </c>
       <c r="B137" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="C137" s="3" t="s">
         <v>350</v>
-      </c>
-      <c r="C137" s="3" t="s">
-        <v>351</v>
       </c>
       <c r="D137" s="16">
         <v>1028470016</v>
@@ -30616,10 +30623,10 @@
         <v>135</v>
       </c>
       <c r="B138" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="C138" s="3" t="s">
         <v>352</v>
-      </c>
-      <c r="C138" s="3" t="s">
-        <v>353</v>
       </c>
       <c r="D138" s="16">
         <v>1022370544</v>
@@ -30646,10 +30653,10 @@
         <v>136</v>
       </c>
       <c r="B139" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="C139" s="3" t="s">
         <v>354</v>
-      </c>
-      <c r="C139" s="3" t="s">
-        <v>355</v>
       </c>
       <c r="D139" s="16">
         <v>1021736512</v>
@@ -30676,10 +30683,10 @@
         <v>137</v>
       </c>
       <c r="B140" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="C140" s="3" t="s">
         <v>356</v>
-      </c>
-      <c r="C140" s="3" t="s">
-        <v>357</v>
       </c>
       <c r="D140" s="16">
         <v>963349356</v>
@@ -30706,10 +30713,10 @@
         <v>138</v>
       </c>
       <c r="B141" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="C141" s="3" t="s">
         <v>358</v>
-      </c>
-      <c r="C141" s="3" t="s">
-        <v>359</v>
       </c>
       <c r="D141" s="16">
         <v>916057056</v>
@@ -30736,10 +30743,10 @@
         <v>139</v>
       </c>
       <c r="B142" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="C142" s="3" t="s">
         <v>360</v>
-      </c>
-      <c r="C142" s="3" t="s">
-        <v>361</v>
       </c>
       <c r="D142" s="16">
         <v>915770679</v>
@@ -30766,10 +30773,10 @@
         <v>140</v>
       </c>
       <c r="B143" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="C143" s="3" t="s">
         <v>362</v>
-      </c>
-      <c r="C143" s="3" t="s">
-        <v>363</v>
       </c>
       <c r="D143" s="16">
         <v>897741791</v>
@@ -30796,10 +30803,10 @@
         <v>141</v>
       </c>
       <c r="B144" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="C144" s="3" t="s">
         <v>364</v>
-      </c>
-      <c r="C144" s="3" t="s">
-        <v>365</v>
       </c>
       <c r="D144" s="16">
         <v>883459968</v>
@@ -30826,10 +30833,10 @@
         <v>142</v>
       </c>
       <c r="B145" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="C145" s="3" t="s">
         <v>366</v>
-      </c>
-      <c r="C145" s="3" t="s">
-        <v>367</v>
       </c>
       <c r="D145" s="16">
         <v>879114752</v>
@@ -30856,10 +30863,10 @@
         <v>143</v>
       </c>
       <c r="B146" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="C146" s="3" t="s">
         <v>368</v>
-      </c>
-      <c r="C146" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="D146" s="16">
         <v>872812480</v>
@@ -30886,10 +30893,10 @@
         <v>144</v>
       </c>
       <c r="B147" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="C147" s="3" t="s">
         <v>370</v>
-      </c>
-      <c r="C147" s="3" t="s">
-        <v>371</v>
       </c>
       <c r="D147" s="16">
         <v>867636904</v>
@@ -30916,10 +30923,10 @@
         <v>145</v>
       </c>
       <c r="B148" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="C148" s="3" t="s">
         <v>372</v>
-      </c>
-      <c r="C148" s="3" t="s">
-        <v>373</v>
       </c>
       <c r="D148" s="16">
         <v>839963968</v>
@@ -30946,10 +30953,10 @@
         <v>146</v>
       </c>
       <c r="B149" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="C149" s="3" t="s">
         <v>374</v>
-      </c>
-      <c r="C149" s="3" t="s">
-        <v>375</v>
       </c>
       <c r="D149" s="16">
         <v>809358135</v>
@@ -30976,10 +30983,10 @@
         <v>147</v>
       </c>
       <c r="B150" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="C150" s="3" t="s">
         <v>376</v>
-      </c>
-      <c r="C150" s="3" t="s">
-        <v>377</v>
       </c>
       <c r="D150" s="16">
         <v>806839340</v>
@@ -31006,10 +31013,10 @@
         <v>148</v>
       </c>
       <c r="B151" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="C151" s="3" t="s">
         <v>378</v>
-      </c>
-      <c r="C151" s="3" t="s">
-        <v>379</v>
       </c>
       <c r="D151" s="16">
         <v>804490880</v>
@@ -31036,10 +31043,10 @@
         <v>149</v>
       </c>
       <c r="B152" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="C152" s="3" t="s">
         <v>380</v>
-      </c>
-      <c r="C152" s="3" t="s">
-        <v>381</v>
       </c>
       <c r="D152" s="16">
         <v>796813376</v>
@@ -31066,10 +31073,10 @@
         <v>150</v>
       </c>
       <c r="B153" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="C153" s="3" t="s">
         <v>382</v>
-      </c>
-      <c r="C153" s="3" t="s">
-        <v>383</v>
       </c>
       <c r="D153" s="16">
         <v>791724160</v>
@@ -31096,10 +31103,10 @@
         <v>151</v>
       </c>
       <c r="B154" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="C154" s="3" t="s">
         <v>384</v>
-      </c>
-      <c r="C154" s="3" t="s">
-        <v>385</v>
       </c>
       <c r="D154" s="16">
         <v>781390144</v>
@@ -31126,10 +31133,10 @@
         <v>152</v>
       </c>
       <c r="B155" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="C155" s="3" t="s">
         <v>386</v>
-      </c>
-      <c r="C155" s="3" t="s">
-        <v>387</v>
       </c>
       <c r="D155" s="16">
         <v>771114578</v>
@@ -31156,10 +31163,10 @@
         <v>153</v>
       </c>
       <c r="B156" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="C156" s="3" t="s">
         <v>388</v>
-      </c>
-      <c r="C156" s="3" t="s">
-        <v>389</v>
       </c>
       <c r="D156" s="16">
         <v>724678791</v>
@@ -31186,10 +31193,10 @@
         <v>154</v>
       </c>
       <c r="B157" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="C157" s="3" t="s">
         <v>390</v>
-      </c>
-      <c r="C157" s="3" t="s">
-        <v>391</v>
       </c>
       <c r="D157" s="16">
         <v>718399128</v>
@@ -31216,10 +31223,10 @@
         <v>155</v>
       </c>
       <c r="B158" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="C158" s="3" t="s">
         <v>392</v>
-      </c>
-      <c r="C158" s="3" t="s">
-        <v>393</v>
       </c>
       <c r="D158" s="16">
         <v>683822012</v>
@@ -31246,10 +31253,10 @@
         <v>156</v>
       </c>
       <c r="B159" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="C159" s="3" t="s">
         <v>394</v>
-      </c>
-      <c r="C159" s="3" t="s">
-        <v>395</v>
       </c>
       <c r="D159" s="16">
         <v>680072870</v>
@@ -31276,10 +31283,10 @@
         <v>157</v>
       </c>
       <c r="B160" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="C160" s="3" t="s">
         <v>396</v>
-      </c>
-      <c r="C160" s="3" t="s">
-        <v>397</v>
       </c>
       <c r="D160" s="16">
         <v>670485458</v>
@@ -31306,10 +31313,10 @@
         <v>158</v>
       </c>
       <c r="B161" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="C161" s="3" t="s">
         <v>398</v>
-      </c>
-      <c r="C161" s="3" t="s">
-        <v>399</v>
       </c>
       <c r="D161" s="16">
         <v>662825024</v>
@@ -31336,10 +31343,10 @@
         <v>159</v>
       </c>
       <c r="B162" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="C162" s="3" t="s">
         <v>400</v>
-      </c>
-      <c r="C162" s="3" t="s">
-        <v>401</v>
       </c>
       <c r="D162" s="16">
         <v>632421708</v>
@@ -31366,10 +31373,10 @@
         <v>160</v>
       </c>
       <c r="B163" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="C163" s="3" t="s">
         <v>402</v>
-      </c>
-      <c r="C163" s="3" t="s">
-        <v>403</v>
       </c>
       <c r="D163" s="16">
         <v>623013781</v>
@@ -31396,10 +31403,10 @@
         <v>161</v>
       </c>
       <c r="B164" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="C164" s="3" t="s">
         <v>404</v>
-      </c>
-      <c r="C164" s="3" t="s">
-        <v>405</v>
       </c>
       <c r="D164" s="16">
         <v>618756316</v>
@@ -31426,10 +31433,10 @@
         <v>162</v>
       </c>
       <c r="B165" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="C165" s="3" t="s">
         <v>406</v>
-      </c>
-      <c r="C165" s="3" t="s">
-        <v>407</v>
       </c>
       <c r="D165" s="16">
         <v>605217437</v>
@@ -31456,10 +31463,10 @@
         <v>163</v>
       </c>
       <c r="B166" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="C166" s="3" t="s">
         <v>408</v>
-      </c>
-      <c r="C166" s="3" t="s">
-        <v>409</v>
       </c>
       <c r="D166" s="16">
         <v>603712925</v>
@@ -31486,10 +31493,10 @@
         <v>164</v>
       </c>
       <c r="B167" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="C167" s="3" t="s">
         <v>410</v>
-      </c>
-      <c r="C167" s="3" t="s">
-        <v>411</v>
       </c>
       <c r="D167" s="16">
         <v>597003776</v>
@@ -31516,10 +31523,10 @@
         <v>165</v>
       </c>
       <c r="B168" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="C168" s="3" t="s">
         <v>412</v>
-      </c>
-      <c r="C168" s="3" t="s">
-        <v>413</v>
       </c>
       <c r="D168" s="16">
         <v>584677952</v>
@@ -31546,10 +31553,10 @@
         <v>166</v>
       </c>
       <c r="B169" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="C169" s="3" t="s">
         <v>414</v>
-      </c>
-      <c r="C169" s="3" t="s">
-        <v>415</v>
       </c>
       <c r="D169" s="16">
         <v>566445210</v>
@@ -31576,10 +31583,10 @@
         <v>167</v>
       </c>
       <c r="B170" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="C170" s="3" t="s">
         <v>416</v>
-      </c>
-      <c r="C170" s="3" t="s">
-        <v>417</v>
       </c>
       <c r="D170" s="16">
         <v>553275584</v>
@@ -31606,10 +31613,10 @@
         <v>168</v>
       </c>
       <c r="B171" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="C171" s="3" t="s">
         <v>418</v>
-      </c>
-      <c r="C171" s="3" t="s">
-        <v>419</v>
       </c>
       <c r="D171" s="16">
         <v>551565170</v>
@@ -31636,10 +31643,10 @@
         <v>169</v>
       </c>
       <c r="B172" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="C172" s="3" t="s">
         <v>420</v>
-      </c>
-      <c r="C172" s="3" t="s">
-        <v>421</v>
       </c>
       <c r="D172" s="16">
         <v>532741248</v>
@@ -31666,10 +31673,10 @@
         <v>170</v>
       </c>
       <c r="B173" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="C173" s="3" t="s">
         <v>422</v>
-      </c>
-      <c r="C173" s="3" t="s">
-        <v>423</v>
       </c>
       <c r="D173" s="16">
         <v>528815488</v>
@@ -31696,10 +31703,10 @@
         <v>171</v>
       </c>
       <c r="B174" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="C174" s="3" t="s">
         <v>424</v>
-      </c>
-      <c r="C174" s="3" t="s">
-        <v>425</v>
       </c>
       <c r="D174" s="16">
         <v>505292285</v>
@@ -31726,10 +31733,10 @@
         <v>172</v>
       </c>
       <c r="B175" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="C175" s="3" t="s">
         <v>426</v>
-      </c>
-      <c r="C175" s="3" t="s">
-        <v>427</v>
       </c>
       <c r="D175" s="16">
         <v>496141728</v>
@@ -31756,10 +31763,10 @@
         <v>173</v>
       </c>
       <c r="B176" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="C176" s="3" t="s">
         <v>428</v>
-      </c>
-      <c r="C176" s="3" t="s">
-        <v>429</v>
       </c>
       <c r="D176" s="16">
         <v>485312008</v>
@@ -31786,10 +31793,10 @@
         <v>174</v>
       </c>
       <c r="B177" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="C177" s="3" t="s">
         <v>430</v>
-      </c>
-      <c r="C177" s="3" t="s">
-        <v>431</v>
       </c>
       <c r="D177" s="16">
         <v>466570608</v>
@@ -31816,10 +31823,10 @@
         <v>175</v>
       </c>
       <c r="B178" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="C178" s="3" t="s">
         <v>432</v>
-      </c>
-      <c r="C178" s="3" t="s">
-        <v>433</v>
       </c>
       <c r="D178" s="16">
         <v>461955072</v>
@@ -31846,10 +31853,10 @@
         <v>176</v>
       </c>
       <c r="B179" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="C179" s="3" t="s">
         <v>434</v>
-      </c>
-      <c r="C179" s="3" t="s">
-        <v>435</v>
       </c>
       <c r="D179" s="16">
         <v>430596743</v>
@@ -31876,10 +31883,10 @@
         <v>177</v>
       </c>
       <c r="B180" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="C180" s="3" t="s">
         <v>436</v>
-      </c>
-      <c r="C180" s="3" t="s">
-        <v>437</v>
       </c>
       <c r="D180" s="16">
         <v>425832064</v>
@@ -31906,10 +31913,10 @@
         <v>178</v>
       </c>
       <c r="B181" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="C181" s="3" t="s">
         <v>438</v>
-      </c>
-      <c r="C181" s="3" t="s">
-        <v>439</v>
       </c>
       <c r="D181" s="16">
         <v>422887239</v>
@@ -31936,10 +31943,10 @@
         <v>179</v>
       </c>
       <c r="B182" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="C182" s="3" t="s">
         <v>440</v>
-      </c>
-      <c r="C182" s="3" t="s">
-        <v>441</v>
       </c>
       <c r="D182" s="16">
         <v>411193379</v>
@@ -31966,10 +31973,10 @@
         <v>180</v>
       </c>
       <c r="B183" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="C183" s="3" t="s">
         <v>442</v>
-      </c>
-      <c r="C183" s="3" t="s">
-        <v>443</v>
       </c>
       <c r="D183" s="16">
         <v>408410272</v>
@@ -31996,10 +32003,10 @@
         <v>181</v>
       </c>
       <c r="B184" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="C184" s="3" t="s">
         <v>444</v>
-      </c>
-      <c r="C184" s="3" t="s">
-        <v>445</v>
       </c>
       <c r="D184" s="16">
         <v>408284160</v>
@@ -32026,10 +32033,10 @@
         <v>182</v>
       </c>
       <c r="B185" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="C185" s="3" t="s">
         <v>446</v>
-      </c>
-      <c r="C185" s="3" t="s">
-        <v>447</v>
       </c>
       <c r="D185" s="16">
         <v>353468063</v>
@@ -32056,10 +32063,10 @@
         <v>183</v>
       </c>
       <c r="B186" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="C186" s="3" t="s">
         <v>448</v>
-      </c>
-      <c r="C186" s="3" t="s">
-        <v>449</v>
       </c>
       <c r="D186" s="16">
         <v>349247553</v>
@@ -32086,10 +32093,10 @@
         <v>184</v>
       </c>
       <c r="B187" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="C187" s="3" t="s">
         <v>450</v>
-      </c>
-      <c r="C187" s="3" t="s">
-        <v>451</v>
       </c>
       <c r="D187" s="16">
         <v>345361752</v>
@@ -32116,10 +32123,10 @@
         <v>185</v>
       </c>
       <c r="B188" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="C188" s="3" t="s">
         <v>452</v>
-      </c>
-      <c r="C188" s="3" t="s">
-        <v>453</v>
       </c>
       <c r="D188" s="16">
         <v>331858169</v>
@@ -32146,10 +32153,10 @@
         <v>186</v>
       </c>
       <c r="B189" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="C189" s="3" t="s">
         <v>454</v>
-      </c>
-      <c r="C189" s="3" t="s">
-        <v>455</v>
       </c>
       <c r="D189" s="16">
         <v>329036001</v>
@@ -32176,10 +32183,10 @@
         <v>187</v>
       </c>
       <c r="B190" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="C190" s="3" t="s">
         <v>456</v>
-      </c>
-      <c r="C190" s="3" t="s">
-        <v>457</v>
       </c>
       <c r="D190" s="16">
         <v>321877568</v>
@@ -32206,10 +32213,10 @@
         <v>188</v>
       </c>
       <c r="B191" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="C191" s="3" t="s">
         <v>458</v>
-      </c>
-      <c r="C191" s="3" t="s">
-        <v>459</v>
       </c>
       <c r="D191" s="16">
         <v>313822272</v>
@@ -32236,10 +32243,10 @@
         <v>189</v>
       </c>
       <c r="B192" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="C192" s="3" t="s">
         <v>460</v>
-      </c>
-      <c r="C192" s="3" t="s">
-        <v>461</v>
       </c>
       <c r="D192" s="16">
         <v>313733984</v>
@@ -32266,10 +32273,10 @@
         <v>190</v>
       </c>
       <c r="B193" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="C193" s="3" t="s">
         <v>462</v>
-      </c>
-      <c r="C193" s="3" t="s">
-        <v>463</v>
       </c>
       <c r="D193" s="16">
         <v>309899296</v>
@@ -32296,10 +32303,10 @@
         <v>191</v>
       </c>
       <c r="B194" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="C194" s="3" t="s">
         <v>464</v>
-      </c>
-      <c r="C194" s="3" t="s">
-        <v>465</v>
       </c>
       <c r="D194" s="16">
         <v>300329354</v>
@@ -32326,10 +32333,10 @@
         <v>192</v>
       </c>
       <c r="B195" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="C195" s="3" t="s">
         <v>466</v>
-      </c>
-      <c r="C195" s="3" t="s">
-        <v>467</v>
       </c>
       <c r="D195" s="16">
         <v>292311584</v>
@@ -32356,10 +32363,10 @@
         <v>193</v>
       </c>
       <c r="B196" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="C196" s="3" t="s">
         <v>468</v>
-      </c>
-      <c r="C196" s="3" t="s">
-        <v>469</v>
       </c>
       <c r="D196" s="16">
         <v>279334304</v>
@@ -32386,10 +32393,10 @@
         <v>194</v>
       </c>
       <c r="B197" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="C197" s="3" t="s">
         <v>470</v>
-      </c>
-      <c r="C197" s="3" t="s">
-        <v>471</v>
       </c>
       <c r="D197" s="16">
         <v>276176433</v>
@@ -32416,10 +32423,10 @@
         <v>195</v>
       </c>
       <c r="B198" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C198" s="3" t="s">
         <v>472</v>
-      </c>
-      <c r="C198" s="3" t="s">
-        <v>473</v>
       </c>
       <c r="D198" s="16">
         <v>273508640</v>
@@ -32446,10 +32453,10 @@
         <v>196</v>
       </c>
       <c r="B199" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="C199" s="3" t="s">
         <v>474</v>
-      </c>
-      <c r="C199" s="3" t="s">
-        <v>475</v>
       </c>
       <c r="D199" s="16">
         <v>272816752</v>
@@ -32476,10 +32483,10 @@
         <v>197</v>
       </c>
       <c r="B200" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="C200" s="3" t="s">
         <v>476</v>
-      </c>
-      <c r="C200" s="3" t="s">
-        <v>477</v>
       </c>
       <c r="D200" s="16">
         <v>261084442</v>
@@ -32506,10 +32513,10 @@
         <v>198</v>
       </c>
       <c r="B201" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="C201" s="3" t="s">
         <v>478</v>
-      </c>
-      <c r="C201" s="3" t="s">
-        <v>479</v>
       </c>
       <c r="D201" s="16">
         <v>250590912</v>
@@ -32536,10 +32543,10 @@
         <v>199</v>
       </c>
       <c r="B202" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="C202" s="3" t="s">
         <v>480</v>
-      </c>
-      <c r="C202" s="3" t="s">
-        <v>481</v>
       </c>
       <c r="D202" s="16">
         <v>248981418</v>
@@ -32566,7 +32573,7 @@
         <v>200</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C203" s="3"/>
       <c r="D203" s="3"/>
@@ -32592,10 +32599,10 @@
         <v>201</v>
       </c>
       <c r="B204" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="C204" s="3" t="s">
         <v>483</v>
-      </c>
-      <c r="C204" s="3" t="s">
-        <v>484</v>
       </c>
       <c r="D204" s="16">
         <v>243907047</v>
@@ -32622,10 +32629,10 @@
         <v>202</v>
       </c>
       <c r="B205" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="C205" s="3" t="s">
         <v>485</v>
-      </c>
-      <c r="C205" s="3" t="s">
-        <v>486</v>
       </c>
       <c r="D205" s="16">
         <v>243504046</v>
@@ -32652,10 +32659,10 @@
         <v>203</v>
       </c>
       <c r="B206" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="C206" s="3" t="s">
         <v>487</v>
-      </c>
-      <c r="C206" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="D206" s="16">
         <v>242971597</v>
@@ -32682,10 +32689,10 @@
         <v>204</v>
       </c>
       <c r="B207" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="C207" s="3" t="s">
         <v>489</v>
-      </c>
-      <c r="C207" s="3" t="s">
-        <v>490</v>
       </c>
       <c r="D207" s="16">
         <v>242794262</v>
@@ -32712,10 +32719,10 @@
         <v>205</v>
       </c>
       <c r="B208" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="C208" s="3" t="s">
         <v>491</v>
-      </c>
-      <c r="C208" s="3" t="s">
-        <v>492</v>
       </c>
       <c r="D208" s="16">
         <v>242517376</v>
@@ -32742,10 +32749,10 @@
         <v>206</v>
       </c>
       <c r="B209" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="C209" s="3" t="s">
         <v>493</v>
-      </c>
-      <c r="C209" s="3" t="s">
-        <v>494</v>
       </c>
       <c r="D209" s="16">
         <v>240572368</v>
@@ -32772,10 +32779,10 @@
         <v>207</v>
       </c>
       <c r="B210" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="C210" s="3" t="s">
         <v>495</v>
-      </c>
-      <c r="C210" s="3" t="s">
-        <v>496</v>
       </c>
       <c r="D210" s="16">
         <v>237904880</v>
@@ -32802,10 +32809,10 @@
         <v>208</v>
       </c>
       <c r="B211" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="C211" s="3" t="s">
         <v>497</v>
-      </c>
-      <c r="C211" s="3" t="s">
-        <v>498</v>
       </c>
       <c r="D211" s="16">
         <v>237335301</v>
@@ -32832,10 +32839,10 @@
         <v>209</v>
       </c>
       <c r="B212" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="C212" s="3" t="s">
         <v>499</v>
-      </c>
-      <c r="C212" s="3" t="s">
-        <v>500</v>
       </c>
       <c r="D212" s="16">
         <v>232812165</v>
@@ -32862,10 +32869,10 @@
         <v>210</v>
       </c>
       <c r="B213" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="C213" s="3" t="s">
         <v>501</v>
-      </c>
-      <c r="C213" s="3" t="s">
-        <v>502</v>
       </c>
       <c r="D213" s="16">
         <v>232725616</v>
@@ -32892,10 +32899,10 @@
         <v>211</v>
       </c>
       <c r="B214" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="C214" s="3" t="s">
         <v>503</v>
-      </c>
-      <c r="C214" s="3" t="s">
-        <v>504</v>
       </c>
       <c r="D214" s="16">
         <v>231534837</v>
@@ -32922,10 +32929,10 @@
         <v>212</v>
       </c>
       <c r="B215" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="C215" s="3" t="s">
         <v>505</v>
-      </c>
-      <c r="C215" s="3" t="s">
-        <v>506</v>
       </c>
       <c r="D215" s="16">
         <v>228693120</v>
@@ -32952,10 +32959,10 @@
         <v>213</v>
       </c>
       <c r="B216" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="C216" s="3" t="s">
         <v>507</v>
-      </c>
-      <c r="C216" s="3" t="s">
-        <v>508</v>
       </c>
       <c r="D216" s="16">
         <v>227761200</v>
@@ -32982,10 +32989,10 @@
         <v>214</v>
       </c>
       <c r="B217" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="C217" s="3" t="s">
         <v>509</v>
-      </c>
-      <c r="C217" s="3" t="s">
-        <v>510</v>
       </c>
       <c r="D217" s="16">
         <v>227467958</v>
@@ -33012,10 +33019,10 @@
         <v>215</v>
       </c>
       <c r="B218" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="C218" s="3" t="s">
         <v>511</v>
-      </c>
-      <c r="C218" s="3" t="s">
-        <v>512</v>
       </c>
       <c r="D218" s="16">
         <v>227159584</v>
@@ -33042,10 +33049,10 @@
         <v>216</v>
       </c>
       <c r="B219" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="C219" s="3" t="s">
         <v>513</v>
-      </c>
-      <c r="C219" s="3" t="s">
-        <v>514</v>
       </c>
       <c r="D219" s="16">
         <v>225610800</v>
@@ -33072,10 +33079,10 @@
         <v>217</v>
       </c>
       <c r="B220" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="C220" s="3" t="s">
         <v>515</v>
-      </c>
-      <c r="C220" s="3" t="s">
-        <v>516</v>
       </c>
       <c r="D220" s="16">
         <v>225375808</v>
@@ -33102,10 +33109,10 @@
         <v>218</v>
       </c>
       <c r="B221" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="C221" s="3" t="s">
         <v>517</v>
-      </c>
-      <c r="C221" s="3" t="s">
-        <v>518</v>
       </c>
       <c r="D221" s="16">
         <v>219778016</v>
@@ -33132,10 +33139,10 @@
         <v>219</v>
       </c>
       <c r="B222" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="C222" s="3" t="s">
         <v>519</v>
-      </c>
-      <c r="C222" s="3" t="s">
-        <v>520</v>
       </c>
       <c r="D222" s="16">
         <v>216765136</v>
@@ -33162,10 +33169,10 @@
         <v>220</v>
       </c>
       <c r="B223" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="C223" s="3" t="s">
         <v>521</v>
-      </c>
-      <c r="C223" s="3" t="s">
-        <v>522</v>
       </c>
       <c r="D223" s="16">
         <v>214474560</v>
@@ -33192,10 +33199,10 @@
         <v>221</v>
       </c>
       <c r="B224" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="C224" s="3" t="s">
         <v>523</v>
-      </c>
-      <c r="C224" s="3" t="s">
-        <v>524</v>
       </c>
       <c r="D224" s="16">
         <v>211498966</v>
@@ -33222,10 +33229,10 @@
         <v>222</v>
       </c>
       <c r="B225" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="C225" s="3" t="s">
         <v>525</v>
-      </c>
-      <c r="C225" s="3" t="s">
-        <v>526</v>
       </c>
       <c r="D225" s="16">
         <v>202001008</v>
@@ -33252,10 +33259,10 @@
         <v>223</v>
       </c>
       <c r="B226" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="C226" s="3" t="s">
         <v>527</v>
-      </c>
-      <c r="C226" s="3" t="s">
-        <v>528</v>
       </c>
       <c r="D226" s="16">
         <v>194964591</v>
@@ -33282,10 +33289,10 @@
         <v>224</v>
       </c>
       <c r="B227" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="C227" s="3" t="s">
         <v>529</v>
-      </c>
-      <c r="C227" s="3" t="s">
-        <v>530</v>
       </c>
       <c r="D227" s="16">
         <v>194849408</v>
@@ -33312,10 +33319,10 @@
         <v>225</v>
       </c>
       <c r="B228" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="C228" s="3" t="s">
         <v>531</v>
-      </c>
-      <c r="C228" s="3" t="s">
-        <v>532</v>
       </c>
       <c r="D228" s="16">
         <v>192622040</v>
@@ -33342,10 +33349,10 @@
         <v>226</v>
       </c>
       <c r="B229" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="C229" s="3" t="s">
         <v>533</v>
-      </c>
-      <c r="C229" s="3" t="s">
-        <v>534</v>
       </c>
       <c r="D229" s="16">
         <v>187924902</v>
@@ -33372,10 +33379,10 @@
         <v>227</v>
       </c>
       <c r="B230" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="C230" s="3" t="s">
         <v>535</v>
-      </c>
-      <c r="C230" s="3" t="s">
-        <v>536</v>
       </c>
       <c r="D230" s="16">
         <v>186182144</v>
@@ -33402,10 +33409,10 @@
         <v>228</v>
       </c>
       <c r="B231" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="C231" s="3" t="s">
         <v>537</v>
-      </c>
-      <c r="C231" s="3" t="s">
-        <v>538</v>
       </c>
       <c r="D231" s="16">
         <v>185994187</v>
@@ -33432,10 +33439,10 @@
         <v>229</v>
       </c>
       <c r="B232" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="C232" s="3" t="s">
         <v>539</v>
-      </c>
-      <c r="C232" s="3" t="s">
-        <v>540</v>
       </c>
       <c r="D232" s="16">
         <v>183320454</v>
@@ -33462,10 +33469,10 @@
         <v>230</v>
       </c>
       <c r="B233" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="C233" s="3" t="s">
         <v>541</v>
-      </c>
-      <c r="C233" s="3" t="s">
-        <v>542</v>
       </c>
       <c r="D233" s="16">
         <v>178256847</v>
@@ -33492,10 +33499,10 @@
         <v>231</v>
       </c>
       <c r="B234" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="C234" s="3" t="s">
         <v>543</v>
-      </c>
-      <c r="C234" s="3" t="s">
-        <v>544</v>
       </c>
       <c r="D234" s="16">
         <v>167549614</v>
@@ -33522,10 +33529,10 @@
         <v>232</v>
       </c>
       <c r="B235" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="C235" s="3" t="s">
         <v>545</v>
-      </c>
-      <c r="C235" s="3" t="s">
-        <v>546</v>
       </c>
       <c r="D235" s="16">
         <v>156949801</v>
@@ -33552,10 +33559,10 @@
         <v>233</v>
       </c>
       <c r="B236" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="C236" s="3" t="s">
         <v>547</v>
-      </c>
-      <c r="C236" s="3" t="s">
-        <v>548</v>
       </c>
       <c r="D236" s="16">
         <v>151567616</v>
@@ -33582,10 +33589,10 @@
         <v>234</v>
       </c>
       <c r="B237" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="C237" s="3" t="s">
         <v>549</v>
-      </c>
-      <c r="C237" s="3" t="s">
-        <v>550</v>
       </c>
       <c r="D237" s="16">
         <v>149217056</v>
@@ -33612,10 +33619,10 @@
         <v>235</v>
       </c>
       <c r="B238" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="C238" s="3" t="s">
         <v>551</v>
-      </c>
-      <c r="C238" s="3" t="s">
-        <v>552</v>
       </c>
       <c r="D238" s="16">
         <v>144474278</v>
@@ -33642,10 +33649,10 @@
         <v>236</v>
       </c>
       <c r="B239" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="C239" s="3" t="s">
         <v>553</v>
-      </c>
-      <c r="C239" s="3" t="s">
-        <v>554</v>
       </c>
       <c r="D239" s="16">
         <v>135180167</v>
@@ -33672,10 +33679,10 @@
         <v>237</v>
       </c>
       <c r="B240" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="C240" s="3" t="s">
         <v>555</v>
-      </c>
-      <c r="C240" s="3" t="s">
-        <v>556</v>
       </c>
       <c r="D240" s="16">
         <v>133508648</v>
@@ -33702,10 +33709,10 @@
         <v>238</v>
       </c>
       <c r="B241" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="C241" s="3" t="s">
         <v>557</v>
-      </c>
-      <c r="C241" s="3" t="s">
-        <v>558</v>
       </c>
       <c r="D241" s="16">
         <v>133433818</v>
@@ -33732,10 +33739,10 @@
         <v>239</v>
       </c>
       <c r="B242" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="C242" s="3" t="s">
         <v>559</v>
-      </c>
-      <c r="C242" s="3" t="s">
-        <v>560</v>
       </c>
       <c r="D242" s="16">
         <v>132538736</v>
@@ -33762,10 +33769,10 @@
         <v>240</v>
       </c>
       <c r="B243" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="C243" s="3" t="s">
         <v>561</v>
-      </c>
-      <c r="C243" s="3" t="s">
-        <v>562</v>
       </c>
       <c r="D243" s="16">
         <v>130689228</v>
@@ -33792,10 +33799,10 @@
         <v>241</v>
       </c>
       <c r="B244" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="C244" s="3" t="s">
         <v>563</v>
-      </c>
-      <c r="C244" s="3" t="s">
-        <v>564</v>
       </c>
       <c r="D244" s="16">
         <v>129671592</v>
@@ -33822,10 +33829,10 @@
         <v>242</v>
       </c>
       <c r="B245" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="C245" s="3" t="s">
         <v>565</v>
-      </c>
-      <c r="C245" s="3" t="s">
-        <v>566</v>
       </c>
       <c r="D245" s="16">
         <v>129645141</v>
@@ -33852,10 +33859,10 @@
         <v>243</v>
       </c>
       <c r="B246" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="C246" s="3" t="s">
         <v>567</v>
-      </c>
-      <c r="C246" s="3" t="s">
-        <v>568</v>
       </c>
       <c r="D246" s="16">
         <v>128599095</v>
@@ -33882,10 +33889,10 @@
         <v>244</v>
       </c>
       <c r="B247" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="C247" s="3" t="s">
         <v>569</v>
-      </c>
-      <c r="C247" s="3" t="s">
-        <v>570</v>
       </c>
       <c r="D247" s="16">
         <v>125110728</v>
@@ -33912,10 +33919,10 @@
         <v>245</v>
       </c>
       <c r="B248" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="C248" s="3" t="s">
         <v>571</v>
-      </c>
-      <c r="C248" s="3" t="s">
-        <v>572</v>
       </c>
       <c r="D248" s="16">
         <v>124709690</v>
@@ -33942,10 +33949,10 @@
         <v>246</v>
       </c>
       <c r="B249" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="C249" s="3" t="s">
         <v>573</v>
-      </c>
-      <c r="C249" s="3" t="s">
-        <v>574</v>
       </c>
       <c r="D249" s="16">
         <v>121381824</v>
@@ -33972,10 +33979,10 @@
         <v>247</v>
       </c>
       <c r="B250" s="3" t="s">
+        <v>574</v>
+      </c>
+      <c r="C250" s="3" t="s">
         <v>575</v>
-      </c>
-      <c r="C250" s="3" t="s">
-        <v>576</v>
       </c>
       <c r="D250" s="16">
         <v>120855152</v>
@@ -34002,10 +34009,10 @@
         <v>248</v>
       </c>
       <c r="B251" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="C251" s="3" t="s">
         <v>577</v>
-      </c>
-      <c r="C251" s="3" t="s">
-        <v>578</v>
       </c>
       <c r="D251" s="16">
         <v>119170280</v>
@@ -34032,10 +34039,10 @@
         <v>249</v>
       </c>
       <c r="B252" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C252" s="3" t="s">
         <v>579</v>
-      </c>
-      <c r="C252" s="3" t="s">
-        <v>580</v>
       </c>
       <c r="D252" s="16">
         <v>116024520</v>
@@ -34062,10 +34069,10 @@
         <v>250</v>
       </c>
       <c r="B253" s="3" t="s">
+        <v>580</v>
+      </c>
+      <c r="C253" s="3" t="s">
         <v>581</v>
-      </c>
-      <c r="C253" s="3" t="s">
-        <v>582</v>
       </c>
       <c r="D253" s="16">
         <v>115077544</v>
@@ -34092,10 +34099,10 @@
         <v>251</v>
       </c>
       <c r="B254" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="C254" s="3" t="s">
         <v>583</v>
-      </c>
-      <c r="C254" s="3" t="s">
-        <v>584</v>
       </c>
       <c r="D254" s="16">
         <v>113846292</v>
@@ -34122,10 +34129,10 @@
         <v>252</v>
       </c>
       <c r="B255" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="C255" s="3" t="s">
         <v>585</v>
-      </c>
-      <c r="C255" s="3" t="s">
-        <v>586</v>
       </c>
       <c r="D255" s="16">
         <v>107701432</v>
@@ -34152,10 +34159,10 @@
         <v>253</v>
       </c>
       <c r="B256" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="C256" s="3" t="s">
         <v>587</v>
-      </c>
-      <c r="C256" s="3" t="s">
-        <v>588</v>
       </c>
       <c r="D256" s="16">
         <v>107631130</v>
@@ -34182,10 +34189,10 @@
         <v>254</v>
       </c>
       <c r="B257" s="3" t="s">
+        <v>588</v>
+      </c>
+      <c r="C257" s="3" t="s">
         <v>589</v>
-      </c>
-      <c r="C257" s="3" t="s">
-        <v>590</v>
       </c>
       <c r="D257" s="16">
         <v>106719665</v>
@@ -34212,10 +34219,10 @@
         <v>255</v>
       </c>
       <c r="B258" s="3" t="s">
+        <v>590</v>
+      </c>
+      <c r="C258" s="3" t="s">
         <v>591</v>
-      </c>
-      <c r="C258" s="3" t="s">
-        <v>592</v>
       </c>
       <c r="D258" s="16">
         <v>104701384</v>
@@ -34242,10 +34249,10 @@
         <v>256</v>
       </c>
       <c r="B259" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="C259" s="3" t="s">
         <v>593</v>
-      </c>
-      <c r="C259" s="3" t="s">
-        <v>594</v>
       </c>
       <c r="D259" s="16">
         <v>102586404</v>
@@ -34272,10 +34279,10 @@
         <v>257</v>
       </c>
       <c r="B260" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="C260" s="3" t="s">
         <v>595</v>
-      </c>
-      <c r="C260" s="3" t="s">
-        <v>596</v>
       </c>
       <c r="D260" s="16">
         <v>98250251</v>
@@ -34302,10 +34309,10 @@
         <v>258</v>
       </c>
       <c r="B261" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="C261" s="3" t="s">
         <v>597</v>
-      </c>
-      <c r="C261" s="3" t="s">
-        <v>598</v>
       </c>
       <c r="D261" s="16">
         <v>97206232</v>
@@ -34332,10 +34339,10 @@
         <v>259</v>
       </c>
       <c r="B262" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="C262" s="3" t="s">
         <v>599</v>
-      </c>
-      <c r="C262" s="3" t="s">
-        <v>600</v>
       </c>
       <c r="D262" s="16">
         <v>90222136</v>
@@ -34362,10 +34369,10 @@
         <v>260</v>
       </c>
       <c r="B263" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="C263" s="3" t="s">
         <v>601</v>
-      </c>
-      <c r="C263" s="3" t="s">
-        <v>602</v>
       </c>
       <c r="D263" s="16">
         <v>88754032</v>
@@ -34392,10 +34399,10 @@
         <v>261</v>
       </c>
       <c r="B264" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="C264" s="3" t="s">
         <v>603</v>
-      </c>
-      <c r="C264" s="3" t="s">
-        <v>604</v>
       </c>
       <c r="D264" s="16">
         <v>81898152</v>
@@ -34422,10 +34429,10 @@
         <v>262</v>
       </c>
       <c r="B265" s="3" t="s">
+        <v>604</v>
+      </c>
+      <c r="C265" s="3" t="s">
         <v>605</v>
-      </c>
-      <c r="C265" s="3" t="s">
-        <v>606</v>
       </c>
       <c r="D265" s="16">
         <v>75823832</v>
@@ -34452,10 +34459,10 @@
         <v>263</v>
       </c>
       <c r="B266" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="C266" s="3" t="s">
         <v>607</v>
-      </c>
-      <c r="C266" s="3" t="s">
-        <v>608</v>
       </c>
       <c r="D266" s="16">
         <v>71266013</v>
@@ -34482,10 +34489,10 @@
         <v>264</v>
       </c>
       <c r="B267" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="C267" s="3" t="s">
         <v>609</v>
-      </c>
-      <c r="C267" s="3" t="s">
-        <v>610</v>
       </c>
       <c r="D267" s="16">
         <v>70703024</v>
@@ -34512,10 +34519,10 @@
         <v>265</v>
       </c>
       <c r="B268" s="3" t="s">
+        <v>610</v>
+      </c>
+      <c r="C268" s="3" t="s">
         <v>611</v>
-      </c>
-      <c r="C268" s="3" t="s">
-        <v>612</v>
       </c>
       <c r="D268" s="16">
         <v>70007728</v>
@@ -34542,10 +34549,10 @@
         <v>266</v>
       </c>
       <c r="B269" s="3" t="s">
+        <v>612</v>
+      </c>
+      <c r="C269" s="3" t="s">
         <v>613</v>
-      </c>
-      <c r="C269" s="3" t="s">
-        <v>614</v>
       </c>
       <c r="D269" s="16">
         <v>67382016</v>
@@ -34572,10 +34579,10 @@
         <v>267</v>
       </c>
       <c r="B270" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="C270" s="3" t="s">
         <v>615</v>
-      </c>
-      <c r="C270" s="3" t="s">
-        <v>616</v>
       </c>
       <c r="D270" s="16">
         <v>66926006</v>
@@ -34602,10 +34609,10 @@
         <v>268</v>
       </c>
       <c r="B271" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="C271" s="3" t="s">
         <v>617</v>
-      </c>
-      <c r="C271" s="3" t="s">
-        <v>618</v>
       </c>
       <c r="D271" s="16">
         <v>66158509</v>
@@ -34632,10 +34639,10 @@
         <v>269</v>
       </c>
       <c r="B272" s="3" t="s">
+        <v>618</v>
+      </c>
+      <c r="C272" s="3" t="s">
         <v>619</v>
-      </c>
-      <c r="C272" s="3" t="s">
-        <v>620</v>
       </c>
       <c r="D272" s="16">
         <v>65394221</v>
@@ -34662,10 +34669,10 @@
         <v>270</v>
       </c>
       <c r="B273" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="C273" s="3" t="s">
         <v>621</v>
-      </c>
-      <c r="C273" s="3" t="s">
-        <v>622</v>
       </c>
       <c r="D273" s="16">
         <v>60616004</v>
@@ -34692,10 +34699,10 @@
         <v>271</v>
       </c>
       <c r="B274" s="3" t="s">
+        <v>622</v>
+      </c>
+      <c r="C274" s="3" t="s">
         <v>623</v>
-      </c>
-      <c r="C274" s="3" t="s">
-        <v>624</v>
       </c>
       <c r="D274" s="16">
         <v>57091332</v>
@@ -34722,10 +34729,10 @@
         <v>272</v>
       </c>
       <c r="B275" s="3" t="s">
+        <v>624</v>
+      </c>
+      <c r="C275" s="3" t="s">
         <v>625</v>
-      </c>
-      <c r="C275" s="3" t="s">
-        <v>626</v>
       </c>
       <c r="D275" s="16">
         <v>55504929</v>
@@ -34752,10 +34759,10 @@
         <v>273</v>
       </c>
       <c r="B276" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="C276" s="3" t="s">
         <v>627</v>
-      </c>
-      <c r="C276" s="3" t="s">
-        <v>628</v>
       </c>
       <c r="D276" s="16">
         <v>54071794</v>
@@ -34782,10 +34789,10 @@
         <v>274</v>
       </c>
       <c r="B277" s="3" t="s">
+        <v>628</v>
+      </c>
+      <c r="C277" s="3" t="s">
         <v>629</v>
-      </c>
-      <c r="C277" s="3" t="s">
-        <v>630</v>
       </c>
       <c r="D277" s="16">
         <v>52325200</v>
@@ -34812,10 +34819,10 @@
         <v>275</v>
       </c>
       <c r="B278" s="3" t="s">
+        <v>630</v>
+      </c>
+      <c r="C278" s="3" t="s">
         <v>631</v>
-      </c>
-      <c r="C278" s="3" t="s">
-        <v>632</v>
       </c>
       <c r="D278" s="16">
         <v>50595568</v>
@@ -34842,10 +34849,10 @@
         <v>276</v>
       </c>
       <c r="B279" s="3" t="s">
+        <v>632</v>
+      </c>
+      <c r="C279" s="3" t="s">
         <v>633</v>
-      </c>
-      <c r="C279" s="3" t="s">
-        <v>634</v>
       </c>
       <c r="D279" s="16">
         <v>48620928</v>
@@ -34872,10 +34879,10 @@
         <v>277</v>
       </c>
       <c r="B280" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="C280" s="3" t="s">
         <v>635</v>
-      </c>
-      <c r="C280" s="3" t="s">
-        <v>636</v>
       </c>
       <c r="D280" s="16">
         <v>46231824</v>
@@ -34902,10 +34909,10 @@
         <v>278</v>
       </c>
       <c r="B281" s="3" t="s">
+        <v>636</v>
+      </c>
+      <c r="C281" s="3" t="s">
         <v>637</v>
-      </c>
-      <c r="C281" s="3" t="s">
-        <v>638</v>
       </c>
       <c r="D281" s="16">
         <v>44511338</v>
@@ -34932,10 +34939,10 @@
         <v>279</v>
       </c>
       <c r="B282" s="3" t="s">
+        <v>638</v>
+      </c>
+      <c r="C282" s="3" t="s">
         <v>639</v>
-      </c>
-      <c r="C282" s="3" t="s">
-        <v>640</v>
       </c>
       <c r="D282" s="16">
         <v>37850618</v>
@@ -34962,10 +34969,10 @@
         <v>280</v>
       </c>
       <c r="B283" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="C283" s="3" t="s">
         <v>641</v>
-      </c>
-      <c r="C283" s="3" t="s">
-        <v>642</v>
       </c>
       <c r="D283" s="16">
         <v>37843452</v>
@@ -34992,10 +34999,10 @@
         <v>281</v>
       </c>
       <c r="B284" s="3" t="s">
+        <v>642</v>
+      </c>
+      <c r="C284" s="3" t="s">
         <v>643</v>
-      </c>
-      <c r="C284" s="3" t="s">
-        <v>644</v>
       </c>
       <c r="D284" s="16">
         <v>21784470</v>
@@ -35022,10 +35029,10 @@
         <v>282</v>
       </c>
       <c r="B285" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="C285" s="3" t="s">
         <v>645</v>
-      </c>
-      <c r="C285" s="3" t="s">
-        <v>646</v>
       </c>
       <c r="D285" s="16">
         <v>20102876</v>
@@ -35052,10 +35059,10 @@
         <v>283</v>
       </c>
       <c r="B286" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="C286" s="3" t="s">
         <v>647</v>
-      </c>
-      <c r="C286" s="3" t="s">
-        <v>648</v>
       </c>
       <c r="D286" s="16">
         <v>17120622</v>
@@ -35082,10 +35089,10 @@
         <v>284</v>
       </c>
       <c r="B287" s="3" t="s">
+        <v>648</v>
+      </c>
+      <c r="C287" s="3" t="s">
         <v>649</v>
-      </c>
-      <c r="C287" s="3" t="s">
-        <v>650</v>
       </c>
       <c r="D287" s="16">
         <v>13246417</v>
@@ -35112,10 +35119,10 @@
         <v>285</v>
       </c>
       <c r="B288" s="3" t="s">
+        <v>650</v>
+      </c>
+      <c r="C288" s="3" t="s">
         <v>651</v>
-      </c>
-      <c r="C288" s="3" t="s">
-        <v>652</v>
       </c>
       <c r="D288" s="16">
         <v>12743325</v>
@@ -35142,10 +35149,10 @@
         <v>286</v>
       </c>
       <c r="B289" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="C289" s="3" t="s">
         <v>653</v>
-      </c>
-      <c r="C289" s="3" t="s">
-        <v>654</v>
       </c>
       <c r="D289" s="16">
         <v>5910458</v>
@@ -35172,10 +35179,10 @@
         <v>287</v>
       </c>
       <c r="B290" s="3" t="s">
+        <v>654</v>
+      </c>
+      <c r="C290" s="3" t="s">
         <v>655</v>
-      </c>
-      <c r="C290" s="3" t="s">
-        <v>656</v>
       </c>
       <c r="D290" s="16">
         <v>5606911</v>
@@ -35202,10 +35209,10 @@
         <v>288</v>
       </c>
       <c r="B291" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C291" s="3" t="s">
         <v>657</v>
-      </c>
-      <c r="C291" s="3" t="s">
-        <v>658</v>
       </c>
       <c r="D291" s="16">
         <v>5021721</v>
@@ -35232,10 +35239,10 @@
         <v>289</v>
       </c>
       <c r="B292" s="3" t="s">
+        <v>658</v>
+      </c>
+      <c r="C292" s="3" t="s">
         <v>659</v>
-      </c>
-      <c r="C292" s="3" t="s">
-        <v>660</v>
       </c>
       <c r="D292" s="16">
         <v>3010600</v>
@@ -35262,10 +35269,10 @@
         <v>290</v>
       </c>
       <c r="B293" s="3" t="s">
+        <v>660</v>
+      </c>
+      <c r="C293" s="3" t="s">
         <v>661</v>
-      </c>
-      <c r="C293" s="3" t="s">
-        <v>662</v>
       </c>
       <c r="D293" s="16">
         <v>1714280</v>
@@ -35292,10 +35299,10 @@
         <v>291</v>
       </c>
       <c r="B294" s="3" t="s">
+        <v>662</v>
+      </c>
+      <c r="C294" s="3" t="s">
         <v>663</v>
-      </c>
-      <c r="C294" s="3" t="s">
-        <v>664</v>
       </c>
       <c r="D294" s="16">
         <v>775193</v>
@@ -35322,10 +35329,10 @@
         <v>292</v>
       </c>
       <c r="B295" s="3" t="s">
+        <v>664</v>
+      </c>
+      <c r="C295" s="3" t="s">
         <v>665</v>
-      </c>
-      <c r="C295" s="3" t="s">
-        <v>666</v>
       </c>
       <c r="D295" s="3">
         <v>473</v>
